--- a/isolated_excel/MPPM Recalculation.xlsx
+++ b/isolated_excel/MPPM Recalculation.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MPPM Summary'!$A$1:$I$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Monthly Inputs'!$A$1:$G$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Monthly Inputs'!$A$1:$G$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source and Method'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,21 +513,21 @@
         <v>46.57265489959113</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.03263370241484307</v>
+        <v>0.03245415728861997</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>47.01293292530011</v>
+        <v>46.70649053326548</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>11.85293292530012</v>
+        <v>11.54649053326548</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>3</v>
@@ -546,21 +546,21 @@
         <v>12.80668196833166</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.009824109332120233</v>
+        <v>0.009968591383249884</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>12.44724565179176</v>
+        <v>12.64046028511974</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>4.077245651791761</v>
+        <v>4.270460285119738</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>3</v>
@@ -576,24 +576,24 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82295882614039</v>
+        <v>27.82298177528853</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.01982792636944819</v>
+        <v>0.02043076663695832</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>26.56767522253958</v>
+        <v>27.46839945977315</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.377675222539576</v>
+        <v>6.278399459773151</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -679,10 +679,10 @@
         <v>0.9631201026442409</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.02285938558352174</v>
+        <v>0.0228591470497912</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9558024313568368</v>
+        <v>0.9558028771487073</v>
       </c>
     </row>
     <row r="3">
@@ -704,10 +704,10 @@
         <v>0.9250752875147531</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.06935283243179036</v>
+        <v>-0.06935277556863939</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.154595552301128</v>
+        <v>1.154595411208053</v>
       </c>
     </row>
     <row r="4">
@@ -729,10 +729,10 @@
         <v>0.9976745395509637</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.0734134415145471</v>
+        <v>0.07341347323291636</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.8678925119844181</v>
+        <v>0.8678924606935867</v>
       </c>
     </row>
     <row r="5">
@@ -754,10 +754,10 @@
         <v>0.9797710949826629</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.04250421205546351</v>
+        <v>-0.04250382596535285</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.090752596947427</v>
+        <v>1.090751717301707</v>
       </c>
     </row>
     <row r="6">
@@ -779,10 +779,10 @@
         <v>0.9724380915636373</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3854462412563477</v>
+        <v>0.3854459413790421</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.5209795094896849</v>
+        <v>0.5209797350198825</v>
       </c>
     </row>
     <row r="7">
@@ -804,10 +804,10 @@
         <v>0.9876324120800218</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.001454503699099385</v>
+        <v>0.001454655740082078</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9970973270586911</v>
+        <v>0.9970970242998092</v>
       </c>
     </row>
     <row r="8">
@@ -829,10 +829,10 @@
         <v>0.9601089735562846</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1241699140486252</v>
+        <v>0.1241696717852019</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7912907403478026</v>
+        <v>0.7912910814009888</v>
       </c>
     </row>
     <row r="9">
@@ -854,10 +854,10 @@
         <v>0.9939038411792369</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.04356164383561634</v>
+        <v>0.04356189773556429</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9182560186693564</v>
+        <v>0.918255571843677</v>
       </c>
     </row>
     <row r="10">
@@ -879,10 +879,10 @@
         <v>0.9599867759537827</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.05506392446076891</v>
+        <v>0.05506341882685883</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8983435477202788</v>
+        <v>0.8983444087738636</v>
       </c>
     </row>
     <row r="11">
@@ -904,10 +904,10 @@
         <v>0.9549146468467293</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1568497101328961</v>
+        <v>0.1568493093612204</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.7472159191580994</v>
+        <v>0.7472164368798553</v>
       </c>
     </row>
     <row r="12">
@@ -929,10 +929,10 @@
         <v>0.9413715807084023</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.02882171416760748</v>
+        <v>-0.02882105628470177</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.060234843454777</v>
+        <v>1.060233407035366</v>
       </c>
     </row>
     <row r="13">
@@ -954,10 +954,10 @@
         <v>0.9781287914115532</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.03592256053872533</v>
+        <v>-0.03592239798838426</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.075910535044374</v>
+        <v>1.075910172232066</v>
       </c>
     </row>
     <row r="14">
@@ -979,10 +979,10 @@
         <v>0.8946259836989391</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2702841717105691</v>
+        <v>0.2702839361416431</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.619723873552168</v>
+        <v>0.6197241034026709</v>
       </c>
     </row>
     <row r="15">
@@ -1004,10 +1004,10 @@
         <v>1.077996580636878</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.01484755857082565</v>
+        <v>-0.01484773445048615</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1.030369807101754</v>
+        <v>1.030370175006522</v>
       </c>
     </row>
     <row r="16">
@@ -1029,10 +1029,10 @@
         <v>1.05283346576593</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.0430167319765653</v>
+        <v>-0.04301657298715189</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.091921232075592</v>
+        <v>1.091920869260737</v>
       </c>
     </row>
     <row r="17">
@@ -1054,10 +1054,10 @@
         <v>0.9923697257955202</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.02888723059494003</v>
+        <v>-0.02888710249012416</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1.060377906432487</v>
+        <v>1.060377626672002</v>
       </c>
     </row>
     <row r="18">
@@ -1079,10 +1079,10 @@
         <v>0.9535211430164198</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.1220363097163717</v>
+        <v>0.1220360864374244</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.7943029539970288</v>
+        <v>0.7943032701208098</v>
       </c>
     </row>
     <row r="19">
@@ -1104,10 +1104,10 @@
         <v>0.9878038066806144</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-0.06062873724857742</v>
+        <v>-0.06062882526693603</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.1332493007963</v>
+        <v>1.13324951316549</v>
       </c>
     </row>
     <row r="20">
@@ -1129,10 +1129,10 @@
         <v>0.9295283057246148</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.03360051231671157</v>
+        <v>0.03360086837908227</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.9360403453593833</v>
+        <v>0.936039700451475</v>
       </c>
     </row>
     <row r="21">
@@ -1154,10 +1154,10 @@
         <v>0.9378842120205459</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.146914757174905</v>
+        <v>0.1469144753935934</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.7602172474565654</v>
+        <v>0.7602176210067193</v>
       </c>
     </row>
     <row r="22">
@@ -1179,10 +1179,10 @@
         <v>0.9887123252954994</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.001211391988220623</v>
+        <v>0.001211166243223705</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.9975816113352296</v>
+        <v>0.9975820611885488</v>
       </c>
     </row>
     <row r="23">
@@ -1204,10 +1204,10 @@
         <v>1.152111238395737</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-0.2497688045483735</v>
+        <v>-0.2497683912712815</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.776682246670818</v>
+        <v>1.77668028924364</v>
       </c>
     </row>
     <row r="24">
@@ -1229,10 +1229,10 @@
         <v>0.9604566236375061</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-0.2240500650023255</v>
+        <v>-0.2240500045812026</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1.660858363666864</v>
+        <v>1.660858105013796</v>
       </c>
     </row>
     <row r="25">
@@ -1254,10 +1254,10 @@
         <v>1.208353246583336</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-0.1831363842994731</v>
+        <v>-0.183136818674309</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.498652336911499</v>
+        <v>1.498653930757447</v>
       </c>
     </row>
     <row r="26">
@@ -1279,10 +1279,10 @@
         <v>0.857124786546162</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.07677881889603055</v>
+        <v>0.07677904068510788</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.8624759464859943</v>
+        <v>0.8624755911898426</v>
       </c>
     </row>
     <row r="27">
@@ -1304,10 +1304,10 @@
         <v>0.9387485503786788</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.07421897082719897</v>
+        <v>0.07421900381634172</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.8665913792466923</v>
+        <v>0.8665913260208488</v>
       </c>
     </row>
     <row r="28">
@@ -1329,10 +1329,10 @@
         <v>0.9622415103954454</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.1640088082323901</v>
+        <v>0.1640089866296075</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.738052858486461</v>
+        <v>0.7380526322569942</v>
       </c>
     </row>
     <row r="29">
@@ -1354,10 +1354,10 @@
         <v>0.9236868300043514</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.008019797673586959</v>
+        <v>0.008019546108555708</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.9841513133610053</v>
+        <v>0.9841518045778427</v>
       </c>
     </row>
     <row r="30">
@@ -1379,10 +1379,10 @@
         <v>1.140325898830826</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-0.2507481493818129</v>
+        <v>-0.2507479491647804</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.781329874145614</v>
+        <v>1.781328922122771</v>
       </c>
     </row>
     <row r="31">
@@ -1404,10 +1404,10 @@
         <v>0.8726609769291781</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.2123879532281372</v>
+        <v>0.2123869864642927</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.6803255402541909</v>
+        <v>0.6803266252450468</v>
       </c>
     </row>
     <row r="32">
@@ -1429,10 +1429,10 @@
         <v>0.971861873206222</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.02733922257928567</v>
+        <v>0.02733984435396586</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.947484821632645</v>
+        <v>0.9474836747445984</v>
       </c>
     </row>
     <row r="33">
@@ -1454,10 +1454,10 @@
         <v>1.032451781203036</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-0.006188911095817207</v>
+        <v>-0.006188767205097756</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.012493685649672</v>
+        <v>1.01249339245831</v>
       </c>
     </row>
     <row r="34">
@@ -1479,10 +1479,10 @@
         <v>0.9636033160989426</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.0391620591824553</v>
+        <v>0.03916181922248385</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.9260478682141902</v>
+        <v>0.9260482958943484</v>
       </c>
     </row>
     <row r="35">
@@ -1504,10 +1504,10 @@
         <v>0.9580497393985004</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.1548229768248279</v>
+        <v>0.154822566757649</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.7498409730876247</v>
+        <v>0.7498415056113835</v>
       </c>
     </row>
     <row r="36">
@@ -1529,10 +1529,10 @@
         <v>0.9311717640044544</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.07899645736355199</v>
+        <v>0.07899683685315129</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.8589343327973464</v>
+        <v>0.8589337286128348</v>
       </c>
     </row>
     <row r="37">
@@ -1554,10 +1554,10 @@
         <v>0.9422614020637016</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.08563282285618801</v>
+        <v>0.08563278232560179</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.8484652687409506</v>
+        <v>0.8484653320934874</v>
       </c>
     </row>
     <row r="38">
@@ -1579,10 +1579,10 @@
         <v>1.000784713254058</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.004802197433110722</v>
+        <v>0.004802348231823794</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.9904643481023476</v>
+        <v>0.9904640508085801</v>
       </c>
     </row>
     <row r="39">
@@ -1604,10 +1604,10 @@
         <v>1.187452557550319</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.1429664625194604</v>
+        <v>0.1429661787258361</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.7654785497470101</v>
+        <v>0.7654789298771716</v>
       </c>
     </row>
     <row r="40">
@@ -1629,10 +1629,10 @@
         <v>1.301695888634536</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-0.02395680836540848</v>
+        <v>-0.02395654513128542</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.049692096406897</v>
+        <v>1.049691530213374</v>
       </c>
     </row>
     <row r="41">
@@ -1654,10 +1654,10 @@
         <v>0.7856559601127485</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.1088013721369481</v>
+        <v>0.1088012308531945</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.8133781292768334</v>
+        <v>0.8133783365585703</v>
       </c>
     </row>
     <row r="42">
@@ -1679,10 +1679,10 @@
         <v>0.9111424311350199</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.2146568260115995</v>
+        <v>0.214656969264309</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.6777863366861255</v>
+        <v>0.6777861768142837</v>
       </c>
     </row>
     <row r="43">
@@ -1704,10 +1704,10 @@
         <v>0.9613795399637081</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.07059747096386237</v>
+        <v>0.07059699667439601</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.8724641161024282</v>
+        <v>0.8724648891302492</v>
       </c>
     </row>
     <row r="44">
@@ -1729,10 +1729,10 @@
         <v>0.8960977549701413</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.1176066076792814</v>
+        <v>0.1176071683315141</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.8006119688763823</v>
+        <v>0.8006111656160096</v>
       </c>
     </row>
     <row r="45">
@@ -1754,10 +1754,10 @@
         <v>0.870377843369757</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.2599917862993668</v>
+        <v>0.2599918060250836</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.6298897944995833</v>
+        <v>0.629889774777189</v>
       </c>
     </row>
     <row r="46">
@@ -1779,10 +1779,10 @@
         <v>1.080556042343192</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.01196682233590973</v>
+        <v>0.01196672870330273</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.9764892160972187</v>
+        <v>0.9764893967973003</v>
       </c>
     </row>
     <row r="47">
@@ -1804,10 +1804,10 @@
         <v>1.055384676976521</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-0.07364827523864081</v>
+        <v>-0.07364847598012692</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1.165327971730291</v>
+        <v>1.165328476786283</v>
       </c>
     </row>
     <row r="48">
@@ -1829,10 +1829,10 @@
         <v>0.8124073373168651</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.06921163922267226</v>
+        <v>0.06921160074748678</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.8747272265766223</v>
+        <v>0.8747272895300973</v>
       </c>
     </row>
     <row r="49">
@@ -1854,10 +1854,10 @@
         <v>0.9273208253828208</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>-0.02556768457364667</v>
+        <v>-0.02556732179522692</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1.053165547907032</v>
+        <v>1.053164763726307</v>
       </c>
     </row>
     <row r="50">
@@ -1879,10 +1879,10 @@
         <v>1.020502470298805</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>-0.004998041314080548</v>
+        <v>-0.004998199561433103</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1.010071526430646</v>
+        <v>1.010071847718824</v>
       </c>
     </row>
     <row r="51">
@@ -1904,10 +1904,10 @@
         <v>0.947050922347443</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.05579405627172118</v>
+        <v>0.05579413045721027</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.897101482752678</v>
+        <v>0.8971013566828165</v>
       </c>
     </row>
     <row r="52">
@@ -1929,10 +1929,10 @@
         <v>0.9178444163991597</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>-0.0263693823436163</v>
+        <v>-0.02636960049531378</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1.054900637307592</v>
+        <v>1.054901110029871</v>
       </c>
     </row>
     <row r="53">
@@ -1954,10 +1954,10 @@
         <v>0.9012367883774663</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.1244544633344791</v>
+        <v>0.1244545437838092</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.7908903102134078</v>
+        <v>0.7908901970445942</v>
       </c>
     </row>
     <row r="54">
@@ -1979,10 +1979,10 @@
         <v>0.9861767286709302</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.0822810403859966</v>
+        <v>0.08228130993934912</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.8537287346749318</v>
+        <v>0.8537283094150445</v>
       </c>
     </row>
     <row r="55">
@@ -2004,10 +2004,10 @@
         <v>0.9548946305726876</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.2316224879332291</v>
+        <v>0.2316219541977889</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.6592418660285626</v>
+        <v>0.6592424374065292</v>
       </c>
     </row>
     <row r="56">
@@ -2029,10 +2029,10 @@
         <v>0.9541320909722018</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>-0.02517193695026387</v>
+        <v>-0.02517175579831477</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1.052310621428292</v>
+        <v>1.052310230327391</v>
       </c>
     </row>
     <row r="57">
@@ -2054,10 +2054,10 @@
         <v>0.9418538915966996</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.1482098192612498</v>
+        <v>0.1482099974588429</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.7585033214914518</v>
+        <v>0.7585030860581146</v>
       </c>
     </row>
     <row r="58">
@@ -2079,10 +2079,10 @@
         <v>1.099935334897597</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>-0.07455892965801925</v>
+        <v>-0.07455865437939457</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1.167622516956459</v>
+        <v>1.167621822322543</v>
       </c>
     </row>
     <row r="59">
@@ -2104,10 +2104,10 @@
         <v>0.8733386651821466</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2341668407136812</v>
+        <v>0.2341664229132356</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.6565264878199312</v>
+        <v>0.6565269323257943</v>
       </c>
     </row>
     <row r="60">
@@ -2129,10 +2129,10 @@
         <v>1.01400288589504</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.2780537130761895</v>
+        <v>0.2780535014795418</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.6122119284073134</v>
+        <v>0.6122121311249654</v>
       </c>
     </row>
     <row r="61">
@@ -2154,10 +2154,10 @@
         <v>0.9160517804201327</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>-0.0998100797688396</v>
+        <v>-0.09980991413127971</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.234047022957714</v>
+        <v>1.234046568821366</v>
       </c>
     </row>
     <row r="62">
@@ -2179,10 +2179,10 @@
         <v>1.112119386768055</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>-0.167454434811324</v>
+        <v>-0.1674542959030992</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1.442726392075237</v>
+        <v>1.442725910644502</v>
       </c>
     </row>
     <row r="63">
@@ -2204,10 +2204,10 @@
         <v>1.062685451631391</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>-0.004124624549298961</v>
+        <v>-0.004124858161063338</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1.008300568817101</v>
+        <v>1.008301041870183</v>
       </c>
     </row>
     <row r="64">
@@ -2229,10 +2229,10 @@
         <v>0.9296802682757126</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.1191571079042555</v>
+        <v>0.1191571387757528</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.7983951413451159</v>
+        <v>0.7983950972983019</v>
       </c>
     </row>
     <row r="65">
@@ -2254,10 +2254,10 @@
         <v>1.200190656587331</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>-0.3202741339540492</v>
+        <v>-0.3202739802562728</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2.164374489962782</v>
+        <v>2.16437351115809</v>
       </c>
     </row>
     <row r="66">
@@ -2279,10 +2279,10 @@
         <v>0.9963421662408478</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.006739661008697384</v>
+        <v>0.006739456291735557</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.986655732764307</v>
+        <v>0.986656134030361</v>
       </c>
     </row>
     <row r="67">
@@ -2304,10 +2304,10 @@
         <v>1.18803474289766</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>-0.1879709813357917</v>
+        <v>-0.1879709377881579</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1.516550585565183</v>
+        <v>1.516550422905518</v>
       </c>
     </row>
     <row r="68">
@@ -2329,10 +2329,10 @@
         <v>0.8382858229126688</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.19816581003128</v>
+        <v>0.1981658545877099</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.6965722267031987</v>
+        <v>0.6965721748960623</v>
       </c>
     </row>
     <row r="69">
@@ -2354,10 +2354,10 @@
         <v>1.086837917632202</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>-0.1689697973216241</v>
+        <v>-0.1689699318887956</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1.447992739240546</v>
+        <v>1.44799320818219</v>
       </c>
     </row>
     <row r="70">
@@ -2379,10 +2379,10 @@
         <v>1.213175071407492</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>-0.1955340888197248</v>
+        <v>-0.1955341276631157</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1.545200031586336</v>
+        <v>1.545200180805371</v>
       </c>
     </row>
     <row r="71">
@@ -2404,10 +2404,10 @@
         <v>0.855814644350068</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1118708414046692</v>
+        <v>0.1118709031291722</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.8088934482804477</v>
+        <v>0.8088933584704804</v>
       </c>
     </row>
     <row r="72">
@@ -2429,10 +2429,10 @@
         <v>0.8969474204044003</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.2541550494055593</v>
+        <v>0.254154947765054</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.6357663503122962</v>
+        <v>0.6357664533611513</v>
       </c>
     </row>
     <row r="73">
@@ -2454,10 +2454,10 @@
         <v>1.126011828926274</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>-0.1364415619095126</v>
+        <v>-0.1364415308901092</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1.340962199599987</v>
+        <v>1.340962103264075</v>
       </c>
     </row>
     <row r="74">
@@ -2479,10 +2479,10 @@
         <v>0.8852560567072887</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3368687351278623</v>
+        <v>0.3368691557148624</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.5595288272768753</v>
+        <v>0.5595284752147263</v>
       </c>
     </row>
     <row r="75">
@@ -2504,10 +2504,10 @@
         <v>1.050645569002066</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1883094302655908</v>
+        <v>0.1883089093471031</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.7081755242375415</v>
+        <v>0.7081761451229039</v>
       </c>
     </row>
     <row r="76">
@@ -2529,10 +2529,10 @@
         <v>0.9304259309730823</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1966622823795958</v>
+        <v>0.1966627014446669</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.6983237209407104</v>
+        <v>0.6983232318421061</v>
       </c>
     </row>
     <row r="77">
@@ -2554,10 +2554,10 @@
         <v>0.9694982234937056</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>-0.00100795915484464</v>
+        <v>-0.001008053614069193</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1.002018970356102</v>
+        <v>1.002019159846998</v>
       </c>
     </row>
     <row r="78">
@@ -2579,10 +2579,10 @@
         <v>0.9913625810824932</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.3634365332711422</v>
+        <v>0.363436428780211</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.5379354267805821</v>
+        <v>0.5379355092330892</v>
       </c>
     </row>
     <row r="79">
@@ -2604,10 +2604,10 @@
         <v>0.8798812409728222</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1182105081934617</v>
+        <v>0.1182106865009505</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.7997474457488012</v>
+        <v>0.7997471906967809</v>
       </c>
     </row>
     <row r="80">
@@ -2629,10 +2629,10 @@
         <v>0.9387194711195235</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1046523499921483</v>
+        <v>0.1046520284189869</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.8194996235593793</v>
+        <v>0.8195001006854178</v>
       </c>
     </row>
     <row r="81">
@@ -2654,10 +2654,10 @@
         <v>1.032619118725376</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.05619638947121319</v>
+        <v>0.05619655619364927</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.8964181534612434</v>
+        <v>0.8964178704589829</v>
       </c>
     </row>
     <row r="82">
@@ -2679,10 +2679,10 @@
         <v>1.10263682294205</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>-0.1185780613309324</v>
+        <v>-0.1185780952231065</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1.287159268047691</v>
+        <v>1.287159367034627</v>
       </c>
     </row>
     <row r="83">
@@ -2704,10 +2704,10 @@
         <v>1.043418468810109</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>-0.06250716057470163</v>
+        <v>-0.062507267540302</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1.137795158548154</v>
+        <v>1.137795418187391</v>
       </c>
     </row>
     <row r="84">
@@ -2729,10 +2729,10 @@
         <v>0.8396361081156987</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.1468858589700071</v>
+        <v>0.1468859579084962</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.7602555584888074</v>
+        <v>0.7602554273187768</v>
       </c>
     </row>
     <row r="85">
@@ -2754,10 +2754,10 @@
         <v>0.9149756157506371</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.05893412834461786</v>
+        <v>0.05893414142888309</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.8917889960794372</v>
+        <v>0.8917889740414213</v>
       </c>
     </row>
     <row r="86">
@@ -2779,10 +2779,10 @@
         <v>0.9672203593217011</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.2424175241944488</v>
+        <v>0.2424175564739466</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.6478356795456357</v>
+        <v>0.6478356458825407</v>
       </c>
     </row>
     <row r="87">
@@ -2804,10 +2804,10 @@
         <v>0.9011908328520706</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.2858094213803009</v>
+        <v>0.2858097587910202</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.6048487574431439</v>
+        <v>0.6048484400051618</v>
       </c>
     </row>
     <row r="88">
@@ -2829,10 +2829,10 @@
         <v>0.9386281887403397</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.1421812779074114</v>
+        <v>0.1421810468342366</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.7665313573543803</v>
+        <v>0.7665316675063527</v>
       </c>
     </row>
     <row r="89">
@@ -2854,10 +2854,10 @@
         <v>1.086982276900574</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>-0.0437602868993443</v>
+        <v>-0.04376022325813289</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>1.093620009185691</v>
+        <v>1.093619863616972</v>
       </c>
     </row>
     <row r="90">
@@ -2879,10 +2879,10 @@
         <v>0.9077465777794721</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.2688709624204324</v>
+        <v>0.2688708902152934</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.6211050813718927</v>
+        <v>0.6211051520599041</v>
       </c>
     </row>
     <row r="91">
@@ -2904,10 +2904,10 @@
         <v>0.9319221176611617</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1269433351334972</v>
+        <v>0.1269432152707823</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.7874007808292401</v>
+        <v>0.7874009483265888</v>
       </c>
     </row>
     <row r="92">
@@ -2929,10 +2929,10 @@
         <v>0.9760924573374677</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>-0.05277659422323111</v>
+        <v>-0.05277657397651536</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>1.114538713376244</v>
+        <v>1.11453866573015</v>
       </c>
     </row>
     <row r="93">
@@ -2954,10 +2954,10 @@
         <v>0.9531969858300583</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.02008208031891745</v>
+        <v>0.02008212771048568</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.9610141076728321</v>
+        <v>0.9610140183781306</v>
       </c>
     </row>
     <row r="94">
@@ -2979,10 +2979,10 @@
         <v>0.9586163156807694</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.01742813318985359</v>
+        <v>0.01742808690201669</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.9660342304615784</v>
+        <v>0.9660343183609327</v>
       </c>
     </row>
     <row r="95">
@@ -3004,10 +3004,10 @@
         <v>1.018385718385046</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.09321460769799583</v>
+        <v>0.09321497710709581</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.8367373352719453</v>
+        <v>0.8367367697869489</v>
       </c>
     </row>
     <row r="96">
@@ -3029,10 +3029,10 @@
         <v>0.8921825152855977</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04135301258146518</v>
+        <v>0.04135259928286272</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.9221552528954302</v>
+        <v>0.9221559848771878</v>
       </c>
     </row>
     <row r="97">
@@ -3054,10 +3054,10 @@
         <v>1.049436799471192</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>-0.02857691468412549</v>
+        <v>-0.02857691133769347</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1.059700550532997</v>
+        <v>1.059700543231924</v>
       </c>
     </row>
     <row r="98">
@@ -3079,10 +3079,10 @@
         <v>0.9465483128657197</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>-0.1058902751059577</v>
+        <v>-0.1058901794305278</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>1.250887817393697</v>
+        <v>1.250887549687828</v>
       </c>
     </row>
     <row r="99">
@@ -3104,10 +3104,10 @@
         <v>1.026615030088406</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.04039309306242167</v>
+        <v>0.04039318634820721</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.9238576924744808</v>
+        <v>0.9238575268009876</v>
       </c>
     </row>
     <row r="100">
@@ -3129,10 +3129,10 @@
         <v>1.122982133980397</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>-0.1323249309931265</v>
+        <v>-0.1323250437332495</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1.328268159144804</v>
+        <v>1.328268504318131</v>
       </c>
     </row>
     <row r="101">
@@ -3154,10 +3154,10 @@
         <v>1.013702149839987</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.004982410811787075</v>
+        <v>0.004982481462220356</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.990109159950076</v>
+        <v>0.9901090207404083</v>
       </c>
     </row>
     <row r="102">
@@ -3179,10 +3179,10 @@
         <v>0.8850712241425256</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>0.2406355273027898</v>
+        <v>0.2406354069759602</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.6496980641659276</v>
+        <v>0.649698190191852</v>
       </c>
     </row>
     <row r="103">
@@ -3204,10 +3204,10 @@
         <v>0.9055585326855982</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0.1692515633256428</v>
+        <v>0.1692516823827925</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.7314490522216738</v>
+        <v>0.7314489032644627</v>
       </c>
     </row>
     <row r="104">
@@ -3229,10 +3229,10 @@
         <v>0.9565816763960454</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0.1258306729394936</v>
+        <v>0.1258305979143173</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.7889579315325774</v>
+        <v>0.7889580366846491</v>
       </c>
     </row>
     <row r="105">
@@ -3254,10 +3254,10 @@
         <v>0.9606567708776664</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>-0.02074555918313137</v>
+        <v>-0.0207454681313487</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>1.042818916545825</v>
+        <v>1.042818722621746</v>
       </c>
     </row>
     <row r="106">
@@ -3279,10 +3279,10 @@
         <v>0.930810829949856</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.07125121360969189</v>
+        <v>0.07125119707459349</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.8713995796872697</v>
+        <v>0.8713996065879218</v>
       </c>
     </row>
     <row r="107">
@@ -3304,10 +3304,10 @@
         <v>0.9547673052543396</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0.0852717678839181</v>
+        <v>0.08527167560685012</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.8490299080711667</v>
+        <v>0.8490300524515936</v>
       </c>
     </row>
     <row r="108">
@@ -3329,10 +3329,10 @@
         <v>0.9951162119266498</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>-0.125882777513319</v>
+        <v>-0.1258827644807442</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>1.30876190674892</v>
+        <v>1.308761867723177</v>
       </c>
     </row>
     <row r="109">
@@ -3354,10 +3354,10 @@
         <v>0.9987769482420827</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>0.05373101785259271</v>
+        <v>0.05373099736807707</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.9006176866714778</v>
+        <v>0.9006177216874682</v>
       </c>
     </row>
     <row r="110">
@@ -3379,10 +3379,10 @@
         <v>0.9716183111985258</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0.02482573320254033</v>
+        <v>0.02482579447315181</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.9521381268406037</v>
+        <v>0.9521380129908473</v>
       </c>
     </row>
     <row r="111">
@@ -3404,10 +3404,10 @@
         <v>1.015374766883167</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>-0.07293465552553402</v>
+        <v>-0.07293472316669725</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>1.163534611746835</v>
+        <v>1.163534781536039</v>
       </c>
     </row>
     <row r="112">
@@ -3429,10 +3429,10 @@
         <v>1.107555373472521</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>-0.0156925510196515</v>
+        <v>-0.0156925888464382</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>1.032139637087772</v>
+        <v>1.032139716417717</v>
       </c>
     </row>
     <row r="113">
@@ -3454,10 +3454,10 @@
         <v>0.8190929065449872</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>0.1443234085538123</v>
+        <v>0.1443234709050238</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.7636642073707474</v>
+        <v>0.7636641241505943</v>
       </c>
     </row>
     <row r="114">
@@ -3479,10 +3479,10 @@
         <v>0.9024974691223349</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0.05797465881657349</v>
+        <v>0.05797470065579535</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.8934072434521477</v>
+        <v>0.8934071727898472</v>
       </c>
     </row>
     <row r="115">
@@ -3504,10 +3504,10 @@
         <v>1.019322040242174</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>-0.05123049341072095</v>
+        <v>-0.05123052301166586</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>1.110909201347264</v>
+        <v>1.110909270666447</v>
       </c>
     </row>
     <row r="116">
@@ -3529,14 +3529,39 @@
         <v>1.001271074036043</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0.003298534030631073</v>
+        <v>0.003298560492809743</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0.9934354299520529</v>
+        <v>0.9934353775479799</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0.9758465393100408</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0.0272330785351429</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0.9476806390547636</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0.09977585001332034</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0.8267831983753214</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G116"/>
+  <autoFilter ref="A1:G117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/isolated_excel/MPPM Recalculation.xlsx
+++ b/isolated_excel/MPPM Recalculation.xlsx
@@ -576,7 +576,7 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82298177528853</v>
+        <v>27.82296061656442</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>116</v>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.02043076663695832</v>
+        <v>0.02043075292818304</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>27.46839945977315</v>
+        <v>27.46837891038678</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6.278399459773151</v>
+        <v>6.278378910386781</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -679,10 +679,10 @@
         <v>0.9631201026442409</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.0228591470497912</v>
+        <v>0.0228595995254095</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9558028771487073</v>
+        <v>0.9558020315245329</v>
       </c>
     </row>
     <row r="3">
@@ -704,10 +704,10 @@
         <v>0.9250752875147531</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.06935277556863939</v>
+        <v>-0.06935273858460167</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.154595411208053</v>
+        <v>1.154595319440525</v>
       </c>
     </row>
     <row r="4">
@@ -729,10 +729,10 @@
         <v>0.9976745395509637</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.07341347323291636</v>
+        <v>0.07341314465886306</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.8678924606935867</v>
+        <v>0.867892992021135</v>
       </c>
     </row>
     <row r="5">
@@ -754,10 +754,10 @@
         <v>0.9797710949826629</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.04250382596535285</v>
+        <v>-0.04250417050352995</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.090751717301707</v>
+        <v>1.090752502277817</v>
       </c>
     </row>
     <row r="6">
@@ -779,10 +779,10 @@
         <v>0.9724380915636373</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3854459413790421</v>
+        <v>0.3854458842745316</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.5209797350198825</v>
+        <v>0.5209797779667686</v>
       </c>
     </row>
     <row r="7">
@@ -804,10 +804,10 @@
         <v>0.9876324120800218</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.001454655740082078</v>
+        <v>0.001454723004039815</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9970970242998092</v>
+        <v>0.9970968903572788</v>
       </c>
     </row>
     <row r="8">
@@ -829,10 +829,10 @@
         <v>0.9601089735562846</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1241696717852019</v>
+        <v>0.1241698810152463</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7912910814009888</v>
+        <v>0.791290786851463</v>
       </c>
     </row>
     <row r="9">
@@ -854,10 +854,10 @@
         <v>0.9939038411792369</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.04356189773556429</v>
+        <v>0.04356201169344254</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.918255571843677</v>
+        <v>0.9182553712950756</v>
       </c>
     </row>
     <row r="10">
@@ -879,10 +879,10 @@
         <v>0.9599867759537827</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.05506341882685883</v>
+        <v>0.05506317790412329</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8983444087738636</v>
+        <v>0.8983448190461991</v>
       </c>
     </row>
     <row r="11">
@@ -904,10 +904,10 @@
         <v>0.9549146468467293</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1568493093612204</v>
+        <v>0.1568500668719666</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.7472164368798553</v>
+        <v>0.7472154583186544</v>
       </c>
     </row>
     <row r="12">
@@ -929,10 +929,10 @@
         <v>0.9413715807084023</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.02882105628470177</v>
+        <v>-0.02882187930417091</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.060233407035366</v>
+        <v>1.060235204013875</v>
       </c>
     </row>
     <row r="13">
@@ -954,10 +954,10 @@
         <v>0.9781287914115532</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.03592239798838426</v>
+        <v>-0.03592230858882117</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.075910172232066</v>
+        <v>1.075909972692349</v>
       </c>
     </row>
     <row r="14">
@@ -979,10 +979,10 @@
         <v>0.8946259836989391</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2702839361416431</v>
+        <v>0.2702847624139151</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6197241034026709</v>
+        <v>0.6197232971886761</v>
       </c>
     </row>
     <row r="15">
@@ -1004,10 +1004,10 @@
         <v>1.077996580636878</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.01484773445048615</v>
+        <v>-0.01484819817920868</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1.030370175006522</v>
+        <v>1.030371145034403</v>
       </c>
     </row>
     <row r="16">
@@ -1029,10 +1029,10 @@
         <v>1.05283346576593</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.04301657298715189</v>
+        <v>-0.04301656955288269</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.091920869260737</v>
+        <v>1.091920861423715</v>
       </c>
     </row>
     <row r="17">
@@ -1054,10 +1054,10 @@
         <v>0.9923697257955202</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.02888710249012416</v>
+        <v>-0.02888743377860092</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1.060377626672002</v>
+        <v>1.060378350153421</v>
       </c>
     </row>
     <row r="18">
@@ -1079,10 +1079,10 @@
         <v>0.9535211430164198</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.1220360864374244</v>
+        <v>0.1220366333256104</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.7943032701208098</v>
+        <v>0.7943024958235082</v>
       </c>
     </row>
     <row r="19">
@@ -1104,10 +1104,10 @@
         <v>0.9878038066806144</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-0.06062882526693603</v>
+        <v>-0.06062896446669497</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.13324951316549</v>
+        <v>1.133249849024411</v>
       </c>
     </row>
     <row r="20">
@@ -1129,10 +1129,10 @@
         <v>0.9295283057246148</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.03360086837908227</v>
+        <v>0.03360053962341936</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.936039700451475</v>
+        <v>0.9360402959008568</v>
       </c>
     </row>
     <row r="21">
@@ -1154,10 +1154,10 @@
         <v>0.9378842120205459</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.1469144753935934</v>
+        <v>0.146914667857688</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.7602176210067193</v>
+        <v>0.7602173658620464</v>
       </c>
     </row>
     <row r="22">
@@ -1179,10 +1179,10 @@
         <v>0.9887123252954994</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.001211166243223705</v>
+        <v>0.001211441341556485</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.9975820611885488</v>
+        <v>0.9975815129864152</v>
       </c>
     </row>
     <row r="23">
@@ -1204,10 +1204,10 @@
         <v>1.152111238395737</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-0.2497683912712815</v>
+        <v>-0.249768751839513</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.77668028924364</v>
+        <v>1.776681997022743</v>
       </c>
     </row>
     <row r="24">
@@ -1229,10 +1229,10 @@
         <v>0.9604566236375061</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-0.2240500045812026</v>
+        <v>-0.2240498830397153</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1.660858105013796</v>
+        <v>1.660857584714504</v>
       </c>
     </row>
     <row r="25">
@@ -1254,10 +1254,10 @@
         <v>1.208353246583336</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-0.183136818674309</v>
+        <v>-0.1831367812965286</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.498653930757447</v>
+        <v>1.498653793607542</v>
       </c>
     </row>
     <row r="26">
@@ -1279,10 +1279,10 @@
         <v>0.857124786546162</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.07677904068510788</v>
+        <v>0.07677919063725391</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.8624755911898426</v>
+        <v>0.8624753509733564</v>
       </c>
     </row>
     <row r="27">
@@ -1304,10 +1304,10 @@
         <v>0.9387485503786788</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.07421900381634172</v>
+        <v>0.07421899883953387</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.8665913260208488</v>
+        <v>0.8665913340506054</v>
       </c>
     </row>
     <row r="28">
@@ -1329,10 +1329,10 @@
         <v>0.9622415103954454</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.1640089866296075</v>
+        <v>0.1640089139689633</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.7380526322569942</v>
+        <v>0.7380527243995555</v>
       </c>
     </row>
     <row r="29">
@@ -1354,10 +1354,10 @@
         <v>0.9236868300043514</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.008019546108555708</v>
+        <v>0.008019224344257836</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.9841518045778427</v>
+        <v>0.9841524328693619</v>
       </c>
     </row>
     <row r="30">
@@ -1379,10 +1379,10 @@
         <v>1.140325898830826</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-0.2507479491647804</v>
+        <v>-0.2507477632008893</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.781328922122771</v>
+        <v>1.781328037873648</v>
       </c>
     </row>
     <row r="31">
@@ -1404,10 +1404,10 @@
         <v>0.8726609769291781</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.2123869864642927</v>
+        <v>0.212387498580785</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.6803266252450468</v>
+        <v>0.6803260505007316</v>
       </c>
     </row>
     <row r="32">
@@ -1429,10 +1429,10 @@
         <v>0.971861873206222</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.02733984435396586</v>
+        <v>0.02733948334858605</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.9474836747445984</v>
+        <v>0.9474843406330793</v>
       </c>
     </row>
     <row r="33">
@@ -1454,10 +1454,10 @@
         <v>1.032451781203036</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-0.006188767205097756</v>
+        <v>-0.006188881220705822</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.01249339245831</v>
+        <v>1.012493624776211</v>
       </c>
     </row>
     <row r="34">
@@ -1479,10 +1479,10 @@
         <v>0.9636033160989426</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.03916181922248385</v>
+        <v>0.03916170898971694</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.9260482958943484</v>
+        <v>0.9260484923620791</v>
       </c>
     </row>
     <row r="35">
@@ -1504,10 +1504,10 @@
         <v>0.9580497393985004</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.154822566757649</v>
+        <v>0.1548231529536039</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.7498415056113835</v>
+        <v>0.7498407443624517</v>
       </c>
     </row>
     <row r="36">
@@ -1529,10 +1529,10 @@
         <v>0.9311717640044544</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.07899683685315129</v>
+        <v>0.07899700539838994</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.8589337286128348</v>
+        <v>0.8589334602725553</v>
       </c>
     </row>
     <row r="37">
@@ -1554,10 +1554,10 @@
         <v>0.9422614020637016</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.08563278232560179</v>
+        <v>0.08563212417834198</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.8484653320934874</v>
+        <v>0.8484663608311053</v>
       </c>
     </row>
     <row r="38">
@@ -1579,10 +1579,10 @@
         <v>1.000784713254058</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.004802348231823794</v>
+        <v>0.004802512241529833</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.9904640508085801</v>
+        <v>0.9904637274700085</v>
       </c>
     </row>
     <row r="39">
@@ -1604,10 +1604,10 @@
         <v>1.187452557550319</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.1429661787258361</v>
+        <v>0.1429663411715274</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.7654789298771716</v>
+        <v>0.765478712287658</v>
       </c>
     </row>
     <row r="40">
@@ -1629,10 +1629,10 @@
         <v>1.301695888634536</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-0.02395654513128542</v>
+        <v>-0.0239566127896278</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.049691530213374</v>
+        <v>1.049691675740493</v>
       </c>
     </row>
     <row r="41">
@@ -1654,10 +1654,10 @@
         <v>0.7856559601127485</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.1088012308531945</v>
+        <v>0.1088011501242385</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.8133783365585703</v>
+        <v>0.8133784549985382</v>
       </c>
     </row>
     <row r="42">
@@ -1704,10 +1704,10 @@
         <v>0.9613795399637081</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.07059699667439601</v>
+        <v>0.07059732102863103</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.8724648891302492</v>
+        <v>0.8724643604765093</v>
       </c>
     </row>
     <row r="44">
@@ -1729,10 +1729,10 @@
         <v>0.8960977549701413</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.1176071683315141</v>
+        <v>0.1176068297349091</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.8006111656160096</v>
+        <v>0.8006116507316272</v>
       </c>
     </row>
     <row r="45">
@@ -1829,10 +1829,10 @@
         <v>0.8124073373168651</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.06921160074748678</v>
+        <v>0.06921175375168209</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.8747272895300973</v>
+        <v>0.8747270391831757</v>
       </c>
     </row>
     <row r="49">
@@ -1854,10 +1854,10 @@
         <v>0.9273208253828208</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>-0.02556732179522692</v>
+        <v>-0.02556760433653082</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1.053164763726307</v>
+        <v>1.053165374466652</v>
       </c>
     </row>
     <row r="50">
@@ -1879,10 +1879,10 @@
         <v>1.020502470298805</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>-0.004998199561433103</v>
+        <v>-0.004998053440725236</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1.010071847718824</v>
+        <v>1.010071551051259</v>
       </c>
     </row>
     <row r="51">
@@ -1904,10 +1904,10 @@
         <v>0.947050922347443</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.05579413045721027</v>
+        <v>0.05579390906862258</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.8971013566828165</v>
+        <v>0.8971017329078004</v>
       </c>
     </row>
     <row r="52">
@@ -1929,10 +1929,10 @@
         <v>0.9178444163991597</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>-0.02636960049531378</v>
+        <v>-0.02636918664632026</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1.054901110029871</v>
+        <v>1.05490021324299</v>
       </c>
     </row>
     <row r="53">
@@ -1954,10 +1954,10 @@
         <v>0.9012367883774663</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.1244545437838092</v>
+        <v>0.1244544451908152</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.7908901970445942</v>
+        <v>0.7908903357362703</v>
       </c>
     </row>
     <row r="54">
@@ -1979,10 +1979,10 @@
         <v>0.9861767286709302</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.08228130993934912</v>
+        <v>0.08228117174547189</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.8537283094150445</v>
+        <v>0.8537285274360834</v>
       </c>
     </row>
     <row r="55">
@@ -2029,10 +2029,10 @@
         <v>0.9541320909722018</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>-0.02517175579831477</v>
+        <v>-0.02517185159072888</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1.052310230327391</v>
+        <v>1.05231043713993</v>
       </c>
     </row>
     <row r="57">
@@ -2054,10 +2054,10 @@
         <v>0.9418538915966996</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.1482099974588429</v>
+        <v>0.1482103068206888</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.7585030860581146</v>
+        <v>0.7585026773318005</v>
       </c>
     </row>
     <row r="58">
@@ -2079,10 +2079,10 @@
         <v>1.099935334897597</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>-0.07455865437939457</v>
+        <v>-0.07455906952685742</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1.167621822322543</v>
+        <v>1.167622869899606</v>
       </c>
     </row>
     <row r="59">
@@ -2104,10 +2104,10 @@
         <v>0.8733386651821466</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2341664229132356</v>
+        <v>0.2341669502622643</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.6565269323257943</v>
+        <v>0.6565263712691788</v>
       </c>
     </row>
     <row r="60">
@@ -2129,10 +2129,10 @@
         <v>1.01400288589504</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.2780535014795418</v>
+        <v>0.2780537595323853</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.6122121311249654</v>
+        <v>0.6122118839005211</v>
       </c>
     </row>
     <row r="61">
@@ -2154,10 +2154,10 @@
         <v>0.9160517804201327</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>-0.09980991413127971</v>
+        <v>-0.09981023079284457</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.234046568821366</v>
+        <v>1.234047437027604</v>
       </c>
     </row>
     <row r="62">
@@ -2179,10 +2179,10 @@
         <v>1.112119386768055</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>-0.1674542959030992</v>
+        <v>-0.1674544261615176</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1.442725910644502</v>
+        <v>1.442726362096569</v>
       </c>
     </row>
     <row r="63">
@@ -2204,10 +2204,10 @@
         <v>1.062685451631391</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>-0.004124858161063338</v>
+        <v>-0.004124624119425047</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1.008301041870183</v>
+        <v>1.008300567946626</v>
       </c>
     </row>
     <row r="64">
@@ -2229,10 +2229,10 @@
         <v>0.9296802682757126</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.1191571387757528</v>
+        <v>0.1191572079686052</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.7983950972983019</v>
+        <v>0.7983949985753844</v>
       </c>
     </row>
     <row r="65">
@@ -2254,10 +2254,10 @@
         <v>1.200190656587331</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>-0.3202739802562728</v>
+        <v>-0.3202740756754329</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2.16437351115809</v>
+        <v>2.164374118822766</v>
       </c>
     </row>
     <row r="66">
@@ -2279,10 +2279,10 @@
         <v>0.9963421662408478</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.006739456291735557</v>
+        <v>0.006739353030370099</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.986656134030361</v>
+        <v>0.9866563364332264</v>
       </c>
     </row>
     <row r="67">
@@ -2304,10 +2304,10 @@
         <v>1.18803474289766</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>-0.1879709377881579</v>
+        <v>-0.1879709570683575</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1.516550422905518</v>
+        <v>1.516550494921157</v>
       </c>
     </row>
     <row r="68">
@@ -2329,10 +2329,10 @@
         <v>0.8382858229126688</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.1981658545877099</v>
+        <v>0.1981662585587558</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.6965721748960623</v>
+        <v>0.69657170518672</v>
       </c>
     </row>
     <row r="69">
@@ -2354,10 +2354,10 @@
         <v>1.086837917632202</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>-0.1689699318887956</v>
+        <v>-0.1689700016846472</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1.44799320818219</v>
+        <v>1.447993451407882</v>
       </c>
     </row>
     <row r="70">
@@ -2379,10 +2379,10 @@
         <v>1.213175071407492</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>-0.1955341276631157</v>
+        <v>-0.1955342297154857</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1.545200180805371</v>
+        <v>1.545200572845297</v>
       </c>
     </row>
     <row r="71">
@@ -2454,10 +2454,10 @@
         <v>1.126011828926274</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>-0.1364415308901092</v>
+        <v>-0.1364415874322625</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1.340962103264075</v>
+        <v>1.340962278865137</v>
       </c>
     </row>
     <row r="74">
@@ -2479,10 +2479,10 @@
         <v>0.8852560567072887</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3368691557148624</v>
+        <v>0.3368688503927728</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.5595284752147263</v>
+        <v>0.559528730791663</v>
       </c>
     </row>
     <row r="75">
@@ -2504,10 +2504,10 @@
         <v>1.050645569002066</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1883089093471031</v>
+        <v>0.1883093564995657</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.7081761451229039</v>
+        <v>0.7081756121595877</v>
       </c>
     </row>
     <row r="76">
@@ -2529,10 +2529,10 @@
         <v>0.9304259309730823</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1966627014446669</v>
+        <v>0.1966625203708421</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.6983232318421061</v>
+        <v>0.698323443176657</v>
       </c>
     </row>
     <row r="77">
@@ -2554,10 +2554,10 @@
         <v>0.9694982234937056</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>-0.001008053614069193</v>
+        <v>-0.001007915914793878</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1.002019159846998</v>
+        <v>1.002018883613973</v>
       </c>
     </row>
     <row r="78">
@@ -2579,10 +2579,10 @@
         <v>0.9913625810824932</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.363436428780211</v>
+        <v>0.3634364726737245</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.5379355092330892</v>
+        <v>0.5379354745972559</v>
       </c>
     </row>
     <row r="79">
@@ -2604,10 +2604,10 @@
         <v>0.8798812409728222</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1182106865009505</v>
+        <v>0.1182105733971262</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.7997471906967809</v>
+        <v>0.799747352481104</v>
       </c>
     </row>
     <row r="80">
@@ -2654,10 +2654,10 @@
         <v>1.032619118725376</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.05619655619364927</v>
+        <v>0.05619663807868869</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.8964178704589829</v>
+        <v>0.8964177314636346</v>
       </c>
     </row>
     <row r="82">
@@ -2679,10 +2679,10 @@
         <v>1.10263682294205</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>-0.1185780952231065</v>
+        <v>-0.1185779309735295</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1.287159367034627</v>
+        <v>1.287158887320381</v>
       </c>
     </row>
     <row r="83">
@@ -2704,10 +2704,10 @@
         <v>1.043418468810109</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>-0.062507267540302</v>
+        <v>-0.06250733900434413</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1.137795418187391</v>
+        <v>1.137795591653203</v>
       </c>
     </row>
     <row r="84">
@@ -2729,10 +2729,10 @@
         <v>0.8396361081156987</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.1468859579084962</v>
+        <v>0.1468856488778802</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.7602554273187768</v>
+        <v>0.7602558370235017</v>
       </c>
     </row>
     <row r="85">
@@ -2754,10 +2754,10 @@
         <v>0.9149756157506371</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.05893414142888309</v>
+        <v>0.05893430986310011</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.8917889740414213</v>
+        <v>0.8917886903453238</v>
       </c>
     </row>
     <row r="86">
@@ -2779,10 +2779,10 @@
         <v>0.9672203593217011</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.2424175564739466</v>
+        <v>0.2424175377463125</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.6478356458825407</v>
+        <v>0.6478356654128977</v>
       </c>
     </row>
     <row r="87">
@@ -2804,10 +2804,10 @@
         <v>0.9011908328520706</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.2858097587910202</v>
+        <v>0.2858094301189487</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.6048484400051618</v>
+        <v>0.6048487492217697</v>
       </c>
     </row>
     <row r="88">
@@ -2829,10 +2829,10 @@
         <v>0.9386281887403397</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.1421810468342366</v>
+        <v>0.1421812677718244</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.7665316675063527</v>
+        <v>0.766531370958605</v>
       </c>
     </row>
     <row r="89">
@@ -2879,10 +2879,10 @@
         <v>0.9077465777794721</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.2688708902152934</v>
+        <v>0.2688710673211081</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.6211051520599041</v>
+        <v>0.6211049786753434</v>
       </c>
     </row>
     <row r="91">
@@ -2904,10 +2904,10 @@
         <v>0.9319221176611617</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1269432152707823</v>
+        <v>0.1269429881861628</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.7874009483265888</v>
+        <v>0.7874012656570388</v>
       </c>
     </row>
     <row r="92">
@@ -2929,10 +2929,10 @@
         <v>0.9760924573374677</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>-0.05277657397651536</v>
+        <v>-0.05277645338988224</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>1.11453866573015</v>
+        <v>1.114538381956679</v>
       </c>
     </row>
     <row r="93">
@@ -2954,10 +2954,10 @@
         <v>0.9531969858300583</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.02008212771048568</v>
+        <v>0.02008206101966881</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.9610140183781306</v>
+        <v>0.9610141440362799</v>
       </c>
     </row>
     <row r="94">
@@ -2979,10 +2979,10 @@
         <v>0.9586163156807694</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.01742808690201669</v>
+        <v>0.0174281509928309</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.9660343183609327</v>
+        <v>0.9660341966542078</v>
       </c>
     </row>
     <row r="95">
@@ -3004,10 +3004,10 @@
         <v>1.018385718385046</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.09321497710709581</v>
+        <v>0.09321478225631852</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.8367367697869489</v>
+        <v>0.8367370680610431</v>
       </c>
     </row>
     <row r="96">
@@ -3029,10 +3029,10 @@
         <v>0.8921825152855977</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04135259928286272</v>
+        <v>0.04135271929200823</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.9221559848771878</v>
+        <v>0.9221557723322098</v>
       </c>
     </row>
     <row r="97">
@@ -3054,10 +3054,10 @@
         <v>1.049436799471192</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>-0.02857691133769347</v>
+        <v>-0.02857680067055435</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1.059700543231924</v>
+        <v>1.059700301784075</v>
       </c>
     </row>
     <row r="98">
@@ -3079,10 +3079,10 @@
         <v>0.9465483128657197</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>-0.1058901794305278</v>
+        <v>-0.1058902812899192</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>1.250887549687828</v>
+        <v>1.250887834696813</v>
       </c>
     </row>
     <row r="99">
@@ -3104,10 +3104,10 @@
         <v>1.026615030088406</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.04039318634820721</v>
+        <v>0.04039305893354816</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.9238575268009876</v>
+        <v>0.9238577530866169</v>
       </c>
     </row>
     <row r="100">
@@ -3129,10 +3129,10 @@
         <v>1.122982133980397</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>-0.1323250437332495</v>
+        <v>-0.1323248762370933</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1.328268504318131</v>
+        <v>1.328267991499816</v>
       </c>
     </row>
     <row r="101">
@@ -3154,10 +3154,10 @@
         <v>1.013702149839987</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.004982481462220356</v>
+        <v>0.004982410538207693</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.9901090207404083</v>
+        <v>0.9901091604891371</v>
       </c>
     </row>
     <row r="102">
@@ -3229,10 +3229,10 @@
         <v>0.9565816763960454</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0.1258305979143173</v>
+        <v>0.125830694731885</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.7889580366846491</v>
+        <v>0.7889579009892995</v>
       </c>
     </row>
     <row r="105">
@@ -3254,10 +3254,10 @@
         <v>0.9606567708776664</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>-0.0207454681313487</v>
+        <v>-0.02074546634730989</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>1.042818722621746</v>
+        <v>1.042818718822061</v>
       </c>
     </row>
     <row r="106">
@@ -3279,10 +3279,10 @@
         <v>0.930810829949856</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.07125119707459349</v>
+        <v>0.07125110299903326</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.8713996065879218</v>
+        <v>0.8713997596377708</v>
       </c>
     </row>
     <row r="107">
@@ -3329,10 +3329,10 @@
         <v>0.9951162119266498</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>-0.1258827644807442</v>
+        <v>-0.1258826889444383</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>1.308761867723177</v>
+        <v>1.308761641531495</v>
       </c>
     </row>
     <row r="109">
@@ -3354,10 +3354,10 @@
         <v>0.9987769482420827</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>0.05373099736807707</v>
+        <v>0.05373090631056576</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.9006177216874682</v>
+        <v>0.9006178773401333</v>
       </c>
     </row>
     <row r="110">
@@ -3404,10 +3404,10 @@
         <v>1.015374766883167</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>-0.07293472316669725</v>
+        <v>-0.07293464314527709</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>1.163534781536039</v>
+        <v>1.163534580670585</v>
       </c>
     </row>
     <row r="112">
@@ -3429,10 +3429,10 @@
         <v>1.107555373472521</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>-0.0156925888464382</v>
+        <v>-0.01569258749190239</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>1.032139716417717</v>
+        <v>1.032139713576999</v>
       </c>
     </row>
     <row r="113">
@@ -3454,10 +3454,10 @@
         <v>0.8190929065449872</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>0.1443234709050238</v>
+        <v>0.1443234582488593</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.7636641241505943</v>
+        <v>0.7636641410427741</v>
       </c>
     </row>
     <row r="114">
@@ -3479,10 +3479,10 @@
         <v>0.9024974691223349</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0.05797470065579535</v>
+        <v>0.05797461957992356</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.8934071727898472</v>
+        <v>0.8934073097189698</v>
       </c>
     </row>
     <row r="115">

--- a/isolated_excel/MPPM Recalculation.xlsx
+++ b/isolated_excel/MPPM Recalculation.xlsx
@@ -576,7 +576,7 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82296061656442</v>
+        <v>27.82296363114063</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>116</v>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.02043075292818304</v>
+        <v>0.02043075488133247</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>27.46837891038678</v>
+        <v>27.46838183814793</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6.278378910386781</v>
+        <v>6.278381838147926</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -679,10 +679,10 @@
         <v>0.9631201026442409</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.0228595995254095</v>
+        <v>0.02285923588240113</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9558020315245329</v>
+        <v>0.9558027111308282</v>
       </c>
     </row>
     <row r="3">
@@ -704,10 +704,10 @@
         <v>0.9250752875147531</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.06935273858460167</v>
+        <v>-0.06935267436157733</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.154595319440525</v>
+        <v>1.154595160085635</v>
       </c>
     </row>
     <row r="4">
@@ -729,10 +729,10 @@
         <v>0.9976745395509637</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.07341314465886306</v>
+        <v>0.07341354770182096</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.867892992021135</v>
+        <v>0.867892340272154</v>
       </c>
     </row>
     <row r="5">
@@ -754,10 +754,10 @@
         <v>0.9797710949826629</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.04250417050352995</v>
+        <v>-0.04250443363410483</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.090752502277817</v>
+        <v>1.090753101780065</v>
       </c>
     </row>
     <row r="6">
@@ -779,10 +779,10 @@
         <v>0.9724380915636373</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3854458842745316</v>
+        <v>0.3854460488262499</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.5209797779667686</v>
+        <v>0.5209796542115166</v>
       </c>
     </row>
     <row r="7">
@@ -804,10 +804,10 @@
         <v>0.9876324120800218</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.001454723004039815</v>
+        <v>0.001454924308121219</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9970968903572788</v>
+        <v>0.9970964895011872</v>
       </c>
     </row>
     <row r="8">
@@ -829,10 +829,10 @@
         <v>0.9601089735562846</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1241698810152463</v>
+        <v>0.1241695964979852</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.791290786851463</v>
+        <v>0.7912911873887425</v>
       </c>
     </row>
     <row r="9">
@@ -854,10 +854,10 @@
         <v>0.9939038411792369</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.04356201169344254</v>
+        <v>0.04356142114270756</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9182553712950756</v>
+        <v>0.9182564105756141</v>
       </c>
     </row>
     <row r="10">
@@ -879,10 +879,10 @@
         <v>0.9599867759537827</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.05506317790412329</v>
+        <v>0.05506412902187185</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8983448190461991</v>
+        <v>0.8983431993696448</v>
       </c>
     </row>
     <row r="11">
@@ -904,10 +904,10 @@
         <v>0.9549146468467293</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1568500668719666</v>
+        <v>0.1568494918456691</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.7472154583186544</v>
+        <v>0.7472162011441442</v>
       </c>
     </row>
     <row r="12">
@@ -929,10 +929,10 @@
         <v>0.9413715807084023</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.02882187930417091</v>
+        <v>-0.02882160676185097</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.060235204013875</v>
+        <v>1.060234608945196</v>
       </c>
     </row>
     <row r="13">
@@ -954,10 +954,10 @@
         <v>0.9781287914115532</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.03592230858882117</v>
+        <v>-0.03592211594956707</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.075909972692349</v>
+        <v>1.075909542721955</v>
       </c>
     </row>
     <row r="14">
@@ -979,10 +979,10 @@
         <v>0.8946259836989391</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2702847624139151</v>
+        <v>0.2702840090465197</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6197232971886761</v>
+        <v>0.6197240322675426</v>
       </c>
     </row>
     <row r="15">
@@ -1004,10 +1004,10 @@
         <v>1.077996580636878</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.01484819817920868</v>
+        <v>-0.01484773211492074</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1.030371145034403</v>
+        <v>1.030370170120989</v>
       </c>
     </row>
     <row r="16">
@@ -1029,10 +1029,10 @@
         <v>1.05283346576593</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.04301656955288269</v>
+        <v>-0.04301664595456089</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.091920861423715</v>
+        <v>1.091921035772807</v>
       </c>
     </row>
     <row r="17">
@@ -1054,10 +1054,10 @@
         <v>0.9923697257955202</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.02888743377860092</v>
+        <v>-0.02888701665563653</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1.060378350153421</v>
+        <v>1.060377439223234</v>
       </c>
     </row>
     <row r="18">
@@ -1079,10 +1079,10 @@
         <v>0.9535211430164198</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.1220366333256104</v>
+        <v>0.1220359795639541</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.7943024958235082</v>
+        <v>0.7943034214349433</v>
       </c>
     </row>
     <row r="19">
@@ -1104,10 +1104,10 @@
         <v>0.9878038066806144</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-0.06062896446669497</v>
+        <v>-0.06062905031329091</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.133249849024411</v>
+        <v>1.133250056153759</v>
       </c>
     </row>
     <row r="20">
@@ -1129,10 +1129,10 @@
         <v>0.9295283057246148</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.03360053962341936</v>
+        <v>0.0336009553605936</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.9360402959008568</v>
+        <v>0.9360395429087716</v>
       </c>
     </row>
     <row r="21">
@@ -1154,10 +1154,10 @@
         <v>0.9378842120205459</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.146914667857688</v>
+        <v>0.1469146446878671</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.7602173658620464</v>
+        <v>0.760217396577672</v>
       </c>
     </row>
     <row r="22">
@@ -1179,10 +1179,10 @@
         <v>0.9887123252954994</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.001211441341556485</v>
+        <v>0.001211303667462804</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.9975815129864152</v>
+        <v>0.9975817873363744</v>
       </c>
     </row>
     <row r="23">
@@ -1204,10 +1204,10 @@
         <v>1.152111238395737</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-0.249768751839513</v>
+        <v>-0.2497686144983635</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.776681997022743</v>
+        <v>1.776681346526029</v>
       </c>
     </row>
     <row r="24">
@@ -1229,10 +1229,10 @@
         <v>0.9604566236375061</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-0.2240498830397153</v>
+        <v>-0.224050116621593</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1.660857584714504</v>
+        <v>1.660858584640659</v>
       </c>
     </row>
     <row r="25">
@@ -1254,10 +1254,10 @@
         <v>1.208353246583336</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-0.1831367812965286</v>
+        <v>-0.1831364490139741</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.498653793607542</v>
+        <v>1.498652574367416</v>
       </c>
     </row>
     <row r="26">
@@ -1279,10 +1279,10 @@
         <v>0.857124786546162</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.07677919063725391</v>
+        <v>0.07677895184963979</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.8624753509733564</v>
+        <v>0.8624757335002508</v>
       </c>
     </row>
     <row r="27">
@@ -1304,10 +1304,10 @@
         <v>0.9387485503786788</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.07421899883953387</v>
+        <v>0.07421872563992093</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.8665913340506054</v>
+        <v>0.866591774840626</v>
       </c>
     </row>
     <row r="28">
@@ -1329,10 +1329,10 @@
         <v>0.9622415103954454</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.1640089139689633</v>
+        <v>0.1640085077232876</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.7380527243995555</v>
+        <v>0.7380532395689519</v>
       </c>
     </row>
     <row r="29">
@@ -1354,10 +1354,10 @@
         <v>0.9236868300043514</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.008019224344257836</v>
+        <v>0.008020086683348415</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.9841524328693619</v>
+        <v>0.9841507490284105</v>
       </c>
     </row>
     <row r="30">
@@ -1379,10 +1379,10 @@
         <v>1.140325898830826</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-0.2507477632008893</v>
+        <v>-0.2507480555662548</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.781328037873648</v>
+        <v>1.781329428056826</v>
       </c>
     </row>
     <row r="31">
@@ -1404,10 +1404,10 @@
         <v>0.8726609769291781</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.212387498580785</v>
+        <v>0.2123877266768006</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.6803260505007316</v>
+        <v>0.6803257945105999</v>
       </c>
     </row>
     <row r="32">
@@ -1429,10 +1429,10 @@
         <v>0.971861873206222</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.02733948334858605</v>
+        <v>0.02733959727896007</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.9474843406330793</v>
+        <v>0.947484130483992</v>
       </c>
     </row>
     <row r="33">
@@ -1454,10 +1454,10 @@
         <v>1.032451781203036</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-0.006188881220705822</v>
+        <v>-0.006189107840612107</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.012493624776211</v>
+        <v>1.012494086536568</v>
       </c>
     </row>
     <row r="34">
@@ -1479,10 +1479,10 @@
         <v>0.9636033160989426</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.03916170898971694</v>
+        <v>0.03916216789224225</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.9260484923620791</v>
+        <v>0.9260476744610604</v>
       </c>
     </row>
     <row r="35">
@@ -1504,10 +1504,10 @@
         <v>0.9580497393985004</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.1548231529536039</v>
+        <v>0.1548226429742401</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.7498407443624517</v>
+        <v>0.7498414066345201</v>
       </c>
     </row>
     <row r="36">
@@ -1529,10 +1529,10 @@
         <v>0.9311717640044544</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.07899700539838994</v>
+        <v>0.07899662299491528</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.8589334602725553</v>
+        <v>0.8589340690959584</v>
       </c>
     </row>
     <row r="37">
@@ -1554,10 +1554,10 @@
         <v>0.9422614020637016</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.08563212417834198</v>
+        <v>0.08563250893348173</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.8484663608311053</v>
+        <v>0.8484657594273471</v>
       </c>
     </row>
     <row r="38">
@@ -1579,10 +1579,10 @@
         <v>1.000784713254058</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.004802512241529833</v>
+        <v>0.004802349015690988</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.9904637274700085</v>
+        <v>0.990464049263217</v>
       </c>
     </row>
     <row r="39">
@@ -1604,10 +1604,10 @@
         <v>1.187452557550319</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.1429663411715274</v>
+        <v>0.142966526841515</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.765478712287658</v>
+        <v>0.765478463590241</v>
       </c>
     </row>
     <row r="40">
@@ -1629,10 +1629,10 @@
         <v>1.301695888634536</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-0.0239566127896278</v>
+        <v>-0.02395668385282779</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.049691675740493</v>
+        <v>1.049691828591194</v>
       </c>
     </row>
     <row r="41">
@@ -1654,10 +1654,10 @@
         <v>0.7856559601127485</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.1088011501242385</v>
+        <v>0.1088011580457702</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.8133784549985382</v>
+        <v>0.813378443376611</v>
       </c>
     </row>
     <row r="42">
@@ -1679,10 +1679,10 @@
         <v>0.9111424311350199</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.214656969264309</v>
+        <v>0.2146569176961779</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.6777861768142837</v>
+        <v>0.6777862343649659</v>
       </c>
     </row>
     <row r="43">
@@ -1704,10 +1704,10 @@
         <v>0.9613795399637081</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.07059732102863103</v>
+        <v>0.07059765301574861</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.8724643604765093</v>
+        <v>0.8724638193826959</v>
       </c>
     </row>
     <row r="44">
@@ -1729,10 +1729,10 @@
         <v>0.8960977549701413</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.1176068297349091</v>
+        <v>0.1176065030154168</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.8006116507316272</v>
+        <v>0.8006121188310336</v>
       </c>
     </row>
     <row r="45">
@@ -1754,10 +1754,10 @@
         <v>0.870377843369757</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.2599918060250836</v>
+        <v>0.2599920102412046</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.629889774777189</v>
+        <v>0.6298895705955196</v>
       </c>
     </row>
     <row r="46">
@@ -1779,10 +1779,10 @@
         <v>1.080556042343192</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.01196672870330273</v>
+        <v>0.01196672784509833</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.9764893967973003</v>
+        <v>0.9764893984535356</v>
       </c>
     </row>
     <row r="47">
@@ -1804,10 +1804,10 @@
         <v>1.055384676976521</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-0.07364847598012692</v>
+        <v>-0.07364854162864898</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1.165328476786283</v>
+        <v>1.165328641954901</v>
       </c>
     </row>
     <row r="48">
@@ -1829,10 +1829,10 @@
         <v>0.8124073373168651</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.06921175375168209</v>
+        <v>0.06921167724958432</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.8747270391831757</v>
+        <v>0.8747271643566232</v>
       </c>
     </row>
     <row r="49">
@@ -1854,10 +1854,10 @@
         <v>0.9273208253828208</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>-0.02556760433653082</v>
+        <v>-0.0255673199658849</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1.053165374466652</v>
+        <v>1.053164759772009</v>
       </c>
     </row>
     <row r="50">
@@ -1879,10 +1879,10 @@
         <v>1.020502470298805</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>-0.004998053440725236</v>
+        <v>-0.004998346049113311</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1.010071551051259</v>
+        <v>1.010072145131582</v>
       </c>
     </row>
     <row r="51">
@@ -1904,10 +1904,10 @@
         <v>0.947050922347443</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.05579390906862258</v>
+        <v>0.05579398698220239</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.8971017329078004</v>
+        <v>0.8971016005024149</v>
       </c>
     </row>
     <row r="52">
@@ -1929,10 +1929,10 @@
         <v>0.9178444163991597</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>-0.02636918664632026</v>
+        <v>-0.02636932643912504</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1.05490021324299</v>
+        <v>1.054900516165801</v>
       </c>
     </row>
     <row r="53">
@@ -1954,10 +1954,10 @@
         <v>0.9012367883774663</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.1244544451908152</v>
+        <v>0.1244545348492871</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.7908903357362703</v>
+        <v>0.7908902096128674</v>
       </c>
     </row>
     <row r="54">
@@ -1979,10 +1979,10 @@
         <v>0.9861767286709302</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.08228117174547189</v>
+        <v>0.08228136852999035</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.8537285274360834</v>
+        <v>0.85372821697977</v>
       </c>
     </row>
     <row r="55">
@@ -2004,10 +2004,10 @@
         <v>0.9548946305726876</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.2316219541977889</v>
+        <v>0.2316219268710247</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.6592424374065292</v>
+        <v>0.6592424666605762</v>
       </c>
     </row>
     <row r="56">
@@ -2029,10 +2029,10 @@
         <v>0.9541320909722018</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>-0.02517185159072888</v>
+        <v>-0.0251717533870518</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1.05231043713993</v>
+        <v>1.052310225121558</v>
       </c>
     </row>
     <row r="57">
@@ -2054,10 +2054,10 @@
         <v>0.9418538915966996</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.1482103068206888</v>
+        <v>0.1482099828948495</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.7585026773318005</v>
+        <v>0.7585031052999504</v>
       </c>
     </row>
     <row r="58">
@@ -2079,10 +2079,10 @@
         <v>1.099935334897597</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>-0.07455906952685742</v>
+        <v>-0.07455899032591362</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1.167622869899606</v>
+        <v>1.167622670044989</v>
       </c>
     </row>
     <row r="59">
@@ -2104,10 +2104,10 @@
         <v>0.8733386651821466</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2341669502622643</v>
+        <v>0.2341667653086137</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.6565263712691788</v>
+        <v>0.6565265680447874</v>
       </c>
     </row>
     <row r="60">
@@ -2129,10 +2129,10 @@
         <v>1.01400288589504</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.2780537595323853</v>
+        <v>0.2780538012018414</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.6122118839005211</v>
+        <v>0.6122118439796104</v>
       </c>
     </row>
     <row r="61">
@@ -2154,10 +2154,10 @@
         <v>0.9160517804201327</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>-0.09981023079284457</v>
+        <v>-0.09981006661035974</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.234047437027604</v>
+        <v>1.234046986880477</v>
       </c>
     </row>
     <row r="62">
@@ -2179,10 +2179,10 @@
         <v>1.112119386768055</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>-0.1674544261615176</v>
+        <v>-0.1674544152553439</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1.442726362096569</v>
+        <v>1.442726324297739</v>
       </c>
     </row>
     <row r="63">
@@ -2204,10 +2204,10 @@
         <v>1.062685451631391</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>-0.004124624119425047</v>
+        <v>-0.004125014941738225</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1.008300567946626</v>
+        <v>1.008301359344028</v>
       </c>
     </row>
     <row r="64">
@@ -2229,10 +2229,10 @@
         <v>0.9296802682757126</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.1191572079686052</v>
+        <v>0.1191574810683276</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.7983949985753844</v>
+        <v>0.7983946089225794</v>
       </c>
     </row>
     <row r="65">
@@ -2254,10 +2254,10 @@
         <v>1.200190656587331</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>-0.3202740756754329</v>
+        <v>-0.3202741683447206</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2.164374118822766</v>
+        <v>2.164374708975479</v>
       </c>
     </row>
     <row r="66">
@@ -2279,10 +2279,10 @@
         <v>0.9963421662408478</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.006739353030370099</v>
+        <v>0.006739767467747848</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.9866563364332264</v>
+        <v>0.9866555240938436</v>
       </c>
     </row>
     <row r="67">
@@ -2304,10 +2304,10 @@
         <v>1.18803474289766</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>-0.1879709570683575</v>
+        <v>-0.1879712775032717</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1.516550494921157</v>
+        <v>1.516551691814346</v>
       </c>
     </row>
     <row r="68">
@@ -2329,10 +2329,10 @@
         <v>0.8382858229126688</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.1981662585587558</v>
+        <v>0.1981663592620166</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.69657170518672</v>
+        <v>0.6965715880960696</v>
       </c>
     </row>
     <row r="69">
@@ -2354,10 +2354,10 @@
         <v>1.086837917632202</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>-0.1689700016846472</v>
+        <v>-0.168969966786725</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1.447993451407882</v>
+        <v>1.447993329795041</v>
       </c>
     </row>
     <row r="70">
@@ -2379,10 +2379,10 @@
         <v>1.213175071407492</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>-0.1955342297154857</v>
+        <v>-0.195534115260649</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1.545200572845297</v>
+        <v>1.545200133160607</v>
       </c>
     </row>
     <row r="71">
@@ -2404,10 +2404,10 @@
         <v>0.855814644350068</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1118709031291722</v>
+        <v>0.1118708154629613</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.8088933584704804</v>
+        <v>0.8088934860259798</v>
       </c>
     </row>
     <row r="72">
@@ -2429,10 +2429,10 @@
         <v>0.8969474204044003</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.254154947765054</v>
+        <v>0.2541546641145687</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.6357664533611513</v>
+        <v>0.6357667409420831</v>
       </c>
     </row>
     <row r="73">
@@ -2454,10 +2454,10 @@
         <v>1.126011828926274</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>-0.1364415874322625</v>
+        <v>-0.1364413921224097</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1.340962278865137</v>
+        <v>1.340961672298048</v>
       </c>
     </row>
     <row r="74">
@@ -2479,10 +2479,10 @@
         <v>0.8852560567072887</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3368688503927728</v>
+        <v>0.3368689813443158</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.559528730791663</v>
+        <v>0.5595286211756152</v>
       </c>
     </row>
     <row r="75">
@@ -2504,10 +2504,10 @@
         <v>1.050645569002066</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1883093564995657</v>
+        <v>0.1883092401000188</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.7081756121595877</v>
+        <v>0.7081757508967474</v>
       </c>
     </row>
     <row r="76">
@@ -2529,10 +2529,10 @@
         <v>0.9304259309730823</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1966625203708421</v>
+        <v>0.1966624379395134</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.698323443176657</v>
+        <v>0.6983235393837901</v>
       </c>
     </row>
     <row r="77">
@@ -2554,10 +2554,10 @@
         <v>0.9694982234937056</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>-0.001007915914793878</v>
+        <v>-0.00100784709986157</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1.002018883613973</v>
+        <v>1.002018745567124</v>
       </c>
     </row>
     <row r="78">
@@ -2579,10 +2579,10 @@
         <v>0.9913625810824932</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.3634364726737245</v>
+        <v>0.3634361968582969</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.5379354745972559</v>
+        <v>0.5379356922398831</v>
       </c>
     </row>
     <row r="79">
@@ -2604,10 +2604,10 @@
         <v>0.8798812409728222</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1182105733971262</v>
+        <v>0.118210698457627</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.799747352481104</v>
+        <v>0.7997471735938888</v>
       </c>
     </row>
     <row r="80">
@@ -2629,10 +2629,10 @@
         <v>0.9387194711195235</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1046520284189869</v>
+        <v>0.1046521283397153</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.8195001006854178</v>
+        <v>0.8194999524305218</v>
       </c>
     </row>
     <row r="81">
@@ -2679,10 +2679,10 @@
         <v>1.10263682294205</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>-0.1185779309735295</v>
+        <v>-0.1185780860299585</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1.287158887320381</v>
+        <v>1.287159340184724</v>
       </c>
     </row>
     <row r="83">
@@ -2704,10 +2704,10 @@
         <v>1.043418468810109</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>-0.06250733900434413</v>
+        <v>-0.06250726204228019</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1.137795591653203</v>
+        <v>1.137795404841957</v>
       </c>
     </row>
     <row r="84">
@@ -2729,10 +2729,10 @@
         <v>0.8396361081156987</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.1468856488778802</v>
+        <v>0.1468856626590918</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.7602558370235017</v>
+        <v>0.7602558187527242</v>
       </c>
     </row>
     <row r="85">
@@ -2754,10 +2754,10 @@
         <v>0.9149756157506371</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.05893430986310011</v>
+        <v>0.05893439649082755</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.8917886903453238</v>
+        <v>0.8917885444370887</v>
       </c>
     </row>
     <row r="86">
@@ -2779,10 +2779,10 @@
         <v>0.9672203593217011</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.2424175377463125</v>
+        <v>0.2424173832390697</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.6478356654128977</v>
+        <v>0.6478358265428207</v>
       </c>
     </row>
     <row r="87">
@@ -2804,10 +2804,10 @@
         <v>0.9011908328520706</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.2858094301189487</v>
+        <v>0.285809590022434</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.6048487492217697</v>
+        <v>0.6048485987836055</v>
       </c>
     </row>
     <row r="88">
@@ -2829,10 +2829,10 @@
         <v>0.9386281887403397</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.1421812677718244</v>
+        <v>0.1421811710544132</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.766531370958605</v>
+        <v>0.7665315007750209</v>
       </c>
     </row>
     <row r="89">
@@ -2854,10 +2854,10 @@
         <v>1.086982276900574</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>-0.04376022325813289</v>
+        <v>-0.04376022696365323</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>1.093619863616972</v>
+        <v>1.093619872092734</v>
       </c>
     </row>
     <row r="90">
@@ -2879,10 +2879,10 @@
         <v>0.9077465777794721</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.2688710673211081</v>
+        <v>0.2688710911304248</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.6211049786753434</v>
+        <v>0.6211049553663011</v>
       </c>
     </row>
     <row r="91">
@@ -2904,10 +2904,10 @@
         <v>0.9319221176611617</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1269429881861628</v>
+        <v>0.1269431366228349</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.7874012656570388</v>
+        <v>0.787401058230041</v>
       </c>
     </row>
     <row r="92">
@@ -2929,10 +2929,10 @@
         <v>0.9760924573374677</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>-0.05277645338988224</v>
+        <v>-0.05277651204904255</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>1.114538381956679</v>
+        <v>1.114538519997782</v>
       </c>
     </row>
     <row r="93">
@@ -2979,10 +2979,10 @@
         <v>0.9586163156807694</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.0174281509928309</v>
+        <v>0.01742821508364489</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.9660341966542078</v>
+        <v>0.9660340749475063</v>
       </c>
     </row>
     <row r="95">
@@ -3004,10 +3004,10 @@
         <v>1.018385718385046</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.09321478225631852</v>
+        <v>0.09321458740556565</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.8367370680610431</v>
+        <v>0.8367373663352595</v>
       </c>
     </row>
     <row r="96">
@@ -3029,10 +3029,10 @@
         <v>0.8921825152855977</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04135271929200823</v>
+        <v>0.04135272405764212</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.9221557723322098</v>
+        <v>0.922155763891925</v>
       </c>
     </row>
     <row r="97">
@@ -3054,10 +3054,10 @@
         <v>1.049436799471192</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>-0.02857680067055435</v>
+        <v>-0.02857680383306749</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1.059700301784075</v>
+        <v>1.059700308683882</v>
       </c>
     </row>
     <row r="98">
@@ -3079,10 +3079,10 @@
         <v>0.9465483128657197</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>-0.1058902812899192</v>
+        <v>-0.1058901794305278</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>1.250887834696813</v>
+        <v>1.250887549687828</v>
       </c>
     </row>
     <row r="99">
@@ -3104,10 +3104,10 @@
         <v>1.026615030088406</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.04039305893354816</v>
+        <v>0.04039318634820721</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.9238577530866169</v>
+        <v>0.9238575268009876</v>
       </c>
     </row>
     <row r="100">
@@ -3129,10 +3129,10 @@
         <v>1.122982133980397</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>-0.1323248762370933</v>
+        <v>-0.1323249824993521</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1.328267991499816</v>
+        <v>1.328268316839978</v>
       </c>
     </row>
     <row r="101">
@@ -3179,10 +3179,10 @@
         <v>0.8850712241425256</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>0.2406354069759602</v>
+        <v>0.24063554742098</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.649698190191852</v>
+        <v>0.6496980430948739</v>
       </c>
     </row>
     <row r="103">
@@ -3204,10 +3204,10 @@
         <v>0.9055585326855982</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0.1692516823827925</v>
+        <v>0.169251436814627</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.7314489032644627</v>
+        <v>0.731449210504768</v>
       </c>
     </row>
     <row r="104">
@@ -3229,10 +3229,10 @@
         <v>0.9565816763960454</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0.125830694731885</v>
+        <v>0.1258308037320852</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.7889579009892995</v>
+        <v>0.7889577482193367</v>
       </c>
     </row>
     <row r="105">
@@ -3254,10 +3254,10 @@
         <v>0.9606567708776664</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>-0.02074546634730989</v>
+        <v>-0.02074555234387065</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>1.042818718822061</v>
+        <v>1.042818901979416</v>
       </c>
     </row>
     <row r="106">
@@ -3279,10 +3279,10 @@
         <v>0.930810829949856</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.07125110299903326</v>
+        <v>0.07125119707459349</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.8713997596377708</v>
+        <v>0.8713996065879218</v>
       </c>
     </row>
     <row r="107">
@@ -3304,10 +3304,10 @@
         <v>0.9547673052543396</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0.08527167560685012</v>
+        <v>0.08527175758426342</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.8490300524515936</v>
+        <v>0.8490299241864205</v>
       </c>
     </row>
     <row r="108">
@@ -3329,10 +3329,10 @@
         <v>0.9951162119266498</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>-0.1258826889444383</v>
+        <v>-0.1258827549720258</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>1.308761641531495</v>
+        <v>1.308761839249541</v>
       </c>
     </row>
     <row r="109">

--- a/isolated_excel/MPPM Recalculation.xlsx
+++ b/isolated_excel/MPPM Recalculation.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MPPM Summary'!$A$1:$I$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Monthly Inputs'!$A$1:$G$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Monthly Inputs'!$A$1:$G$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source and Method'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,21 +513,21 @@
         <v>46.57265489959113</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>Sept 2026</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.03245415728861997</v>
+        <v>0.03226541457697028</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>46.70649053326548</v>
+        <v>46.38498135854536</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>11.54649053326548</v>
+        <v>11.22498135854536</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>3</v>
@@ -546,21 +546,21 @@
         <v>12.80668196833166</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>Sept 2026</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.009968591383249884</v>
+        <v>0.009852249259162317</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>12.64046028511974</v>
+        <v>12.48485309971457</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>4.270460285119738</v>
+        <v>4.114853099714567</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>3</v>
@@ -576,24 +576,24 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82296363114063</v>
+        <v>27.82295574656268</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>Sept 2026</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.02043075488133247</v>
+        <v>0.0205531804479008</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>27.46838183814793</v>
+        <v>27.65201829092905</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6.278381838147926</v>
+        <v>6.462018290929048</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -679,10 +679,10 @@
         <v>0.9631201026442409</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.02285923588240113</v>
+        <v>0.02285950861465746</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9558027111308282</v>
+        <v>0.9558022014260387</v>
       </c>
     </row>
     <row r="3">
@@ -704,10 +704,10 @@
         <v>0.9250752875147531</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.06935267436157733</v>
+        <v>-0.06935292250664793</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.154595160085635</v>
+        <v>1.154595775801609</v>
       </c>
     </row>
     <row r="4">
@@ -729,10 +729,10 @@
         <v>0.9976745395509637</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.07341354770182096</v>
+        <v>0.0734133566970383</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.867892340272154</v>
+        <v>0.8678926491403109</v>
       </c>
     </row>
     <row r="5">
@@ -754,10 +754,10 @@
         <v>0.9797710949826629</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.04250443363410483</v>
+        <v>-0.04250426325590773</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.090753101780065</v>
+        <v>1.090752713599683</v>
       </c>
     </row>
     <row r="6">
@@ -779,10 +779,10 @@
         <v>0.9724380915636373</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3854460488262499</v>
+        <v>0.3854463275870208</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.5209796542115166</v>
+        <v>0.5209794445625788</v>
       </c>
     </row>
     <row r="7">
@@ -804,10 +804,10 @@
         <v>0.9876324120800218</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.001454924308121219</v>
+        <v>0.001454655740082078</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9970964895011872</v>
+        <v>0.9970970242998092</v>
       </c>
     </row>
     <row r="8">
@@ -829,10 +829,10 @@
         <v>0.9601089735562846</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1241695964979852</v>
+        <v>0.1241699396708196</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7912911873887425</v>
+        <v>0.7912907042774466</v>
       </c>
     </row>
     <row r="9">
@@ -854,10 +854,10 @@
         <v>0.9939038411792369</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.04356142114270756</v>
+        <v>0.04356117246580737</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9182564105756141</v>
+        <v>0.9182568482101122</v>
       </c>
     </row>
     <row r="10">
@@ -879,10 +879,10 @@
         <v>0.9599867759537827</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.05506412902187185</v>
+        <v>0.05506401484726586</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8983431993696448</v>
+        <v>0.8983433937995275</v>
       </c>
     </row>
     <row r="11">
@@ -904,10 +904,10 @@
         <v>0.9549146468467293</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1568494918456691</v>
+        <v>0.1568496170350731</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.7472162011441442</v>
+        <v>0.7472160394229587</v>
       </c>
     </row>
     <row r="12">
@@ -929,10 +929,10 @@
         <v>0.9413715807084023</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.02882160676185097</v>
+        <v>-0.0288214196747697</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.060234608945196</v>
+        <v>1.060234200459706</v>
       </c>
     </row>
     <row r="13">
@@ -954,10 +954,10 @@
         <v>0.9781287914115532</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.03592211594956707</v>
+        <v>-0.03592278326681819</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.075909542721955</v>
+        <v>1.075911032173701</v>
       </c>
     </row>
     <row r="14">
@@ -979,10 +979,10 @@
         <v>0.8946259836989391</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2702840090465197</v>
+        <v>0.2702847435166309</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6197240322675426</v>
+        <v>0.6197233156271994</v>
       </c>
     </row>
     <row r="15">
@@ -1004,10 +1004,10 @@
         <v>1.077996580636878</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.01484773211492074</v>
+        <v>-0.01484796689881163</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1.030370170120989</v>
+        <v>1.030370661241828</v>
       </c>
     </row>
     <row r="16">
@@ -1029,10 +1029,10 @@
         <v>1.05283346576593</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.04301664595456089</v>
+        <v>-0.04301665282311129</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.091921035772807</v>
+        <v>1.091921051446883</v>
       </c>
     </row>
     <row r="17">
@@ -1054,10 +1054,10 @@
         <v>0.9923697257955202</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.02888701665563653</v>
+        <v>-0.02888718832462622</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1.060377439223234</v>
+        <v>1.060377814120852</v>
       </c>
     </row>
     <row r="18">
@@ -1079,10 +1079,10 @@
         <v>0.9535211430164198</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.1220359795639541</v>
+        <v>0.122036107404736</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.7943034214349433</v>
+        <v>0.7943032404347704</v>
       </c>
     </row>
     <row r="19">
@@ -1104,10 +1104,10 @@
         <v>0.9878038066806144</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-0.06062905031329091</v>
+        <v>-0.0606287579879855</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.133250056153759</v>
+        <v>1.133249350835984</v>
       </c>
     </row>
     <row r="20">
@@ -1129,10 +1129,10 @@
         <v>0.9295283057246148</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.0336009553605936</v>
+        <v>0.03360087111769672</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.9360395429087716</v>
+        <v>0.9360396954912394</v>
       </c>
     </row>
     <row r="21">
@@ -1154,10 +1154,10 @@
         <v>0.9378842120205459</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.1469146446878671</v>
+        <v>0.1469147235425563</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.760217396577672</v>
+        <v>0.7602172920420806</v>
       </c>
     </row>
     <row r="22">
@@ -1179,10 +1179,10 @@
         <v>0.9887123252954994</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.001211303667462804</v>
+        <v>0.001211028569177319</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.9975817873363744</v>
+        <v>0.9975823355386397</v>
       </c>
     </row>
     <row r="23">
@@ -1204,10 +1204,10 @@
         <v>1.152111238395737</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-0.2497686144983635</v>
+        <v>-0.2497684599418704</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.776681346526029</v>
+        <v>1.776680614491729</v>
       </c>
     </row>
     <row r="24">
@@ -1229,10 +1229,10 @@
         <v>0.9604566236375061</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-0.224050116621593</v>
+        <v>-0.2240502996866476</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1.660858584640659</v>
+        <v>1.660859368313114</v>
       </c>
     </row>
     <row r="25">
@@ -1254,10 +1254,10 @@
         <v>1.208353246583336</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-0.1831364490139741</v>
+        <v>-0.1831362562963657</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.498652574367416</v>
+        <v>1.498651867231843</v>
       </c>
     </row>
     <row r="26">
@@ -1279,10 +1279,10 @@
         <v>0.857124786546162</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.07677895184963979</v>
+        <v>0.07677880744130383</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.8624757335002508</v>
+        <v>0.8624759648359586</v>
       </c>
     </row>
     <row r="27">
@@ -1304,10 +1304,10 @@
         <v>0.9387485503786788</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.07421872563992093</v>
+        <v>0.07421907087205204</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.866591774840626</v>
+        <v>0.8665912178308218</v>
       </c>
     </row>
     <row r="28">
@@ -1329,10 +1329,10 @@
         <v>0.9622415103954454</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.1640085077232876</v>
+        <v>0.1640086642779561</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.7380532395689519</v>
+        <v>0.7380530410383462</v>
       </c>
     </row>
     <row r="29">
@@ -1354,10 +1354,10 @@
         <v>0.9236868300043514</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.008020086683348415</v>
+        <v>0.008019976847981169</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.9841507490284105</v>
+        <v>0.984150963497503</v>
       </c>
     </row>
     <row r="30">
@@ -1379,10 +1379,10 @@
         <v>1.140325898830826</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-0.2507480555662548</v>
+        <v>-0.2507481618085182</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.781329428056826</v>
+        <v>1.781329933234055</v>
       </c>
     </row>
     <row r="31">
@@ -1404,10 +1404,10 @@
         <v>0.8726609769291781</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.2123877266768006</v>
+        <v>0.2123872145602557</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.6803257945105999</v>
+        <v>0.68032636925465</v>
       </c>
     </row>
     <row r="32">
@@ -1429,10 +1429,10 @@
         <v>0.971861873206222</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.02733959727896007</v>
+        <v>0.0273398411515744</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.947484130483992</v>
+        <v>0.9474836806515311</v>
       </c>
     </row>
     <row r="33">
@@ -1454,10 +1454,10 @@
         <v>1.032451781203036</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-0.006189107840612107</v>
+        <v>-0.006188994530671899</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.012494086536568</v>
+        <v>1.012493855656376</v>
       </c>
     </row>
     <row r="34">
@@ -1479,10 +1479,10 @@
         <v>0.9636033160989426</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.03916216789224225</v>
+        <v>0.03916182371534838</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.9260476744610604</v>
+        <v>0.9260482878867227</v>
       </c>
     </row>
     <row r="35">
@@ -1504,10 +1504,10 @@
         <v>0.9580497393985004</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.1548226429742401</v>
+        <v>0.1548229150566363</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.7498414066345201</v>
+        <v>0.7498410533013468</v>
       </c>
     </row>
     <row r="36">
@@ -1529,10 +1529,10 @@
         <v>0.9311717640044544</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.07899662299491528</v>
+        <v>0.07899691734969516</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.8589340690959584</v>
+        <v>0.8589336004545558</v>
       </c>
     </row>
     <row r="37">
@@ -1554,10 +1554,10 @@
         <v>0.9422614020637016</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.08563250893348173</v>
+        <v>0.08563267096236871</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.8484657594273471</v>
+        <v>0.8484655061631334</v>
       </c>
     </row>
     <row r="38">
@@ -1579,10 +1579,10 @@
         <v>1.000784713254058</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.004802349015690988</v>
+        <v>0.00480210260927838</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.990464049263217</v>
+        <v>0.9904645350438945</v>
       </c>
     </row>
     <row r="39">
@@ -1604,10 +1604,10 @@
         <v>1.187452557550319</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.142966526841515</v>
+        <v>0.1429665964522182</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.765478463590241</v>
+        <v>0.7654783703495589</v>
       </c>
     </row>
     <row r="40">
@@ -1629,10 +1629,10 @@
         <v>1.301695888634536</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-0.02395668385282779</v>
+        <v>-0.02395682257433085</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.049691828591194</v>
+        <v>1.049692126969056</v>
       </c>
     </row>
     <row r="41">
@@ -1679,10 +1679,10 @@
         <v>0.9111424311350199</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.2146569176961779</v>
+        <v>0.2146573116753359</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.6777862343649659</v>
+        <v>0.6777857946794612</v>
       </c>
     </row>
     <row r="43">
@@ -1704,10 +1704,10 @@
         <v>0.9613795399637081</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.07059765301574861</v>
+        <v>0.07059708952683108</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.8724638193826959</v>
+        <v>0.8724647377932303</v>
       </c>
     </row>
     <row r="44">
@@ -1729,10 +1729,10 @@
         <v>0.8960977549701413</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.1176065030154168</v>
+        <v>0.117606930723466</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.8006121188310336</v>
+        <v>0.8006115060428116</v>
       </c>
     </row>
     <row r="45">
@@ -1754,10 +1754,10 @@
         <v>0.870377843369757</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.2599920102412046</v>
+        <v>0.2599917825318532</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.6298895705955196</v>
+        <v>0.6298897982664624</v>
       </c>
     </row>
     <row r="46">
@@ -1779,10 +1779,10 @@
         <v>1.080556042343192</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.01196672784509833</v>
+        <v>0.01196658441332676</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.9764893984535356</v>
+        <v>0.9764896752603323</v>
       </c>
     </row>
     <row r="47">
@@ -1804,10 +1804,10 @@
         <v>1.055384676976521</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-0.07364854162864898</v>
+        <v>-0.07364841033159564</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1.165328641954901</v>
+        <v>1.165328311617677</v>
       </c>
     </row>
     <row r="48">
@@ -1829,10 +1829,10 @@
         <v>0.8124073373168651</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.06921167724958432</v>
+        <v>0.06921175375168209</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.8747271643566232</v>
+        <v>0.8747270391831757</v>
       </c>
     </row>
     <row r="49">
@@ -1854,10 +1854,10 @@
         <v>0.9273208253828208</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>-0.0255673199658849</v>
+        <v>-0.02556746123653708</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1.053164759772009</v>
+        <v>1.053165065142114</v>
       </c>
     </row>
     <row r="50">
@@ -1879,10 +1879,10 @@
         <v>1.020502470298805</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>-0.004998346049113311</v>
+        <v>-0.004998199561433103</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1.010072145131582</v>
+        <v>1.010071847718824</v>
       </c>
     </row>
     <row r="51">
@@ -1904,10 +1904,10 @@
         <v>0.947050922347443</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.05579398698220239</v>
+        <v>0.0557939828648184</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.8971016005024149</v>
+        <v>0.8971016074994462</v>
       </c>
     </row>
     <row r="52">
@@ -1929,10 +1929,10 @@
         <v>0.9178444163991597</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>-0.02636932643912504</v>
+        <v>-0.02636946438879895</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1.054900516165801</v>
+        <v>1.054900815094783</v>
       </c>
     </row>
     <row r="53">
@@ -1954,10 +1954,10 @@
         <v>0.9012367883774663</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.1244545348492871</v>
+        <v>0.1244546873627026</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.7908902096128674</v>
+        <v>0.7908899950709026</v>
       </c>
     </row>
     <row r="54">
@@ -1979,10 +1979,10 @@
         <v>0.9861767286709302</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.08228136852999035</v>
+        <v>0.08228129943304796</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.85372821697977</v>
+        <v>0.8537283259902673</v>
       </c>
     </row>
     <row r="55">
@@ -2079,10 +2079,10 @@
         <v>1.099935334897597</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>-0.07455899032591362</v>
+        <v>-0.07455890474406701</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1.167622670044989</v>
+        <v>1.167622454088943</v>
       </c>
     </row>
     <row r="59">
@@ -2104,10 +2104,10 @@
         <v>0.8733386651821466</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2341667653086137</v>
+        <v>0.2341668361304334</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.6565265680447874</v>
+        <v>0.6565264926961334</v>
       </c>
     </row>
     <row r="60">
@@ -2129,10 +2129,10 @@
         <v>1.01400288589504</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.2780538012018414</v>
+        <v>0.2780539093935128</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.6122118439796104</v>
+        <v>0.6122117403279266</v>
       </c>
     </row>
     <row r="61">
@@ -2154,10 +2154,10 @@
         <v>0.9160517804201327</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>-0.09981006661035974</v>
+        <v>-0.09981033634665004</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.234046986880477</v>
+        <v>1.234047726429751</v>
       </c>
     </row>
     <row r="62">
@@ -2179,10 +2179,10 @@
         <v>1.112119386768055</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>-0.1674544152553439</v>
+        <v>-0.1674543610323084</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1.442726324297739</v>
+        <v>1.442726136370509</v>
       </c>
     </row>
     <row r="63">
@@ -2204,10 +2204,10 @@
         <v>1.062685451631391</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>-0.004125014941738225</v>
+        <v>-0.004124858483746885</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1.008301359344028</v>
+        <v>1.008301042523602</v>
       </c>
     </row>
     <row r="64">
@@ -2229,10 +2229,10 @@
         <v>0.9296802682757126</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.1191574810683276</v>
+        <v>0.119157305241937</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.7983946089225794</v>
+        <v>0.7983948597878558</v>
       </c>
     </row>
     <row r="65">
@@ -2254,10 +2254,10 @@
         <v>1.200190656587331</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>-0.3202741683447206</v>
+        <v>-0.3202742385341527</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2.164374708975479</v>
+        <v>2.164375155968217</v>
       </c>
     </row>
     <row r="66">
@@ -2279,10 +2279,10 @@
         <v>0.9963421662408478</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.006739767467747848</v>
+        <v>0.006739561640910274</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.9866555240938436</v>
+        <v>0.9866559275352396</v>
       </c>
     </row>
     <row r="67">
@@ -2304,10 +2304,10 @@
         <v>1.18803474289766</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>-0.1879712775032717</v>
+        <v>-0.1879708737784411</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1.516551691814346</v>
+        <v>1.516550183815672</v>
       </c>
     </row>
     <row r="68">
@@ -2329,10 +2329,10 @@
         <v>0.8382858229126688</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.1981663592620166</v>
+        <v>0.1981663848721067</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.6965715880960696</v>
+        <v>0.6965715583184675</v>
       </c>
     </row>
     <row r="69">
@@ -2354,10 +2354,10 @@
         <v>1.086837917632202</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>-0.168969966786725</v>
+        <v>-0.1689701420047741</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1.447993329795041</v>
+        <v>1.447993940397874</v>
       </c>
     </row>
     <row r="70">
@@ -2404,10 +2404,10 @@
         <v>0.855814644350068</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1118708154629613</v>
+        <v>0.1118707366172873</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.8088934860259798</v>
+        <v>0.8088936007475068</v>
       </c>
     </row>
     <row r="72">
@@ -2429,10 +2429,10 @@
         <v>0.8969474204044003</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.2541546641145687</v>
+        <v>0.2541548948752226</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.6357667409420831</v>
+        <v>0.635766506983844</v>
       </c>
     </row>
     <row r="73">
@@ -2454,10 +2454,10 @@
         <v>1.126011828926274</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>-0.1364413921224097</v>
+        <v>-0.1364413766930278</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1.340961672298048</v>
+        <v>1.340961624379565</v>
       </c>
     </row>
     <row r="74">
@@ -2479,10 +2479,10 @@
         <v>0.8852560567072887</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3368689813443158</v>
+        <v>0.3368685443762311</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.5595286211756152</v>
+        <v>0.5595289869500825</v>
       </c>
     </row>
     <row r="75">
@@ -2504,10 +2504,10 @@
         <v>1.050645569002066</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1883092401000188</v>
+        <v>0.1883092769912784</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.7081757508967474</v>
+        <v>0.7081757069258796</v>
       </c>
     </row>
     <row r="76">
@@ -2529,10 +2529,10 @@
         <v>0.9304259309730823</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1966624379395134</v>
+        <v>0.1966628825185215</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.6983235393837901</v>
+        <v>0.6983230205076165</v>
       </c>
     </row>
     <row r="77">
@@ -2554,10 +2554,10 @@
         <v>0.9694982234937056</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>-0.00100784709986157</v>
+        <v>-0.001008053544630072</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1.002018745567124</v>
+        <v>1.002019159707699</v>
       </c>
     </row>
     <row r="78">
@@ -2579,10 +2579,10 @@
         <v>0.9913625810824932</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.3634361968582969</v>
+        <v>0.3634366105814382</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.5379356922398831</v>
+        <v>0.537935365775992</v>
       </c>
     </row>
     <row r="79">
@@ -2604,10 +2604,10 @@
         <v>0.8798812409728222</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.118210698457627</v>
+        <v>0.1182104602933247</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.7997471735938888</v>
+        <v>0.7997475142654433</v>
       </c>
     </row>
     <row r="80">
@@ -2629,10 +2629,10 @@
         <v>0.9387194711195235</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1046521283397153</v>
+        <v>0.1046522093279367</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.8194999524305218</v>
+        <v>0.8194998322662915</v>
       </c>
     </row>
     <row r="81">
@@ -2654,10 +2654,10 @@
         <v>1.032619118725376</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.05619663807868869</v>
+        <v>0.05619630133525821</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.8964177314636346</v>
+        <v>0.896418303067284</v>
       </c>
     </row>
     <row r="82">
@@ -2679,10 +2679,10 @@
         <v>1.10263682294205</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>-0.1185780860299585</v>
+        <v>-0.1185779493598029</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1.287159340184724</v>
+        <v>1.287158941020093</v>
       </c>
     </row>
     <row r="83">
@@ -2729,10 +2729,10 @@
         <v>0.8396361081156987</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.1468856626590918</v>
+        <v>0.1468857564818131</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.7602558187527242</v>
+        <v>0.7602556943649784</v>
       </c>
     </row>
     <row r="85">
@@ -2754,10 +2754,10 @@
         <v>0.9149756157506371</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.05893439649082755</v>
+        <v>0.05893439166961034</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.8917885444370887</v>
+        <v>0.8917885525575281</v>
       </c>
     </row>
     <row r="86">
@@ -2779,10 +2779,10 @@
         <v>0.9672203593217011</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.2424173832390697</v>
+        <v>0.242417441765066</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.6478358265428207</v>
+        <v>0.6478357655082039</v>
       </c>
     </row>
     <row r="87">
@@ -2804,10 +2804,10 @@
         <v>0.9011908328520706</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.285809590022434</v>
+        <v>0.2858093057587894</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.6048485987836055</v>
+        <v>0.604848866220597</v>
       </c>
     </row>
     <row r="88">
@@ -2829,10 +2829,10 @@
         <v>0.9386281887403397</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.1421811710544132</v>
+        <v>0.1421813782406502</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.7665315007750209</v>
+        <v>0.7665312226847528</v>
       </c>
     </row>
     <row r="89">
@@ -2854,10 +2854,10 @@
         <v>1.086982276900574</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>-0.04376022696365323</v>
+        <v>-0.04376030793594532</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>1.093619872092734</v>
+        <v>1.093620057303434</v>
       </c>
     </row>
     <row r="90">
@@ -2879,10 +2879,10 @@
         <v>0.9077465777794721</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.2688710911304248</v>
+        <v>0.2688711796833401</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.6211049553663011</v>
+        <v>0.6211048686740451</v>
       </c>
     </row>
     <row r="91">
@@ -2904,10 +2904,10 @@
         <v>0.9319221176611617</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1269431366228349</v>
+        <v>0.1269429881861628</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.787401058230041</v>
+        <v>0.7874012656570388</v>
       </c>
     </row>
     <row r="92">
@@ -2929,10 +2929,10 @@
         <v>0.9760924573374677</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>-0.05277651204904255</v>
+        <v>-0.05277639146240565</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>1.114538519997782</v>
+        <v>1.114538236224359</v>
       </c>
     </row>
     <row r="93">
@@ -2954,10 +2954,10 @@
         <v>0.9531969858300583</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.02008206101966881</v>
+        <v>0.02008192895097527</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.9610141440362799</v>
+        <v>0.9610143928788231</v>
       </c>
     </row>
     <row r="94">
@@ -2979,10 +2979,10 @@
         <v>0.9586163156807694</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.01742821508364489</v>
+        <v>0.0174282162006334</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.9660340749475063</v>
+        <v>0.9660340728263759</v>
       </c>
     </row>
     <row r="95">
@@ -3004,10 +3004,10 @@
         <v>1.018385718385046</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.09321458740556565</v>
+        <v>0.09321453028446558</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.8367373663352595</v>
+        <v>0.8367374537752976</v>
       </c>
     </row>
     <row r="96">
@@ -3029,10 +3029,10 @@
         <v>0.8921825152855977</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04135272405764212</v>
+        <v>0.04135284406682982</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.922155763891925</v>
+        <v>0.9221555513469486</v>
       </c>
     </row>
     <row r="97">
@@ -3054,10 +3054,10 @@
         <v>1.049436799471192</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>-0.02857680383306749</v>
+        <v>-0.02857691450021882</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1.059700308683882</v>
+        <v>1.059700550131759</v>
       </c>
     </row>
     <row r="98">
@@ -3079,10 +3079,10 @@
         <v>0.9465483128657197</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>-0.1058901794305278</v>
+        <v>-0.1058900206097576</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>1.250887549687828</v>
+        <v>1.250887105297516</v>
       </c>
     </row>
     <row r="99">
@@ -3104,10 +3104,10 @@
         <v>1.026615030088406</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.04039318634820721</v>
+        <v>0.0403930563602144</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.9238575268009876</v>
+        <v>0.9238577576568019</v>
       </c>
     </row>
     <row r="100">
@@ -3129,10 +3129,10 @@
         <v>1.122982133980397</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>-0.1323249824993521</v>
+        <v>-0.132324990602127</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1.328268316839978</v>
+        <v>1.328268341648021</v>
       </c>
     </row>
     <row r="101">
@@ -3154,10 +3154,10 @@
         <v>1.013702149839987</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.004982410538207693</v>
+        <v>0.004982481462220356</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.9901091604891371</v>
+        <v>0.9901090207404083</v>
       </c>
     </row>
     <row r="102">
@@ -3179,10 +3179,10 @@
         <v>0.8850712241425256</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>0.24063554742098</v>
+        <v>0.2406354069759602</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.6496980430948739</v>
+        <v>0.649698190191852</v>
       </c>
     </row>
     <row r="103">
@@ -3204,10 +3204,10 @@
         <v>0.9055585326855982</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0.169251436814627</v>
+        <v>0.1692515691786884</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.731449210504768</v>
+        <v>0.7314490448986909</v>
       </c>
     </row>
     <row r="104">
@@ -3229,10 +3229,10 @@
         <v>0.9565816763960454</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0.1258308037320852</v>
+        <v>0.1258307069145082</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.7889577482193367</v>
+        <v>0.78895788391466</v>
       </c>
     </row>
     <row r="105">
@@ -3254,10 +3254,10 @@
         <v>0.9606567708776664</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>-0.02074555234387065</v>
+        <v>-0.0207454681313487</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>1.042818901979416</v>
+        <v>1.042818722621746</v>
       </c>
     </row>
     <row r="106">
@@ -3304,10 +3304,10 @@
         <v>0.9547673052543396</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0.08527175758426342</v>
+        <v>0.0852718395616765</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.8490299241864205</v>
+        <v>0.8490297959212769</v>
       </c>
     </row>
     <row r="108">
@@ -3329,10 +3329,10 @@
         <v>0.9951162119266498</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>-0.1258827549720258</v>
+        <v>-0.1258828209996035</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>1.308761839249541</v>
+        <v>1.308762036967603</v>
       </c>
     </row>
     <row r="109">
@@ -3404,10 +3404,10 @@
         <v>1.015374766883167</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>-0.07293464314527709</v>
+        <v>-0.07293472316669725</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>1.163534580670585</v>
+        <v>1.163534781536039</v>
       </c>
     </row>
     <row r="112">
@@ -3429,10 +3429,10 @@
         <v>1.107555373472521</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>-0.01569258749190239</v>
+        <v>-0.0156925888464382</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>1.032139713576999</v>
+        <v>1.032139716417717</v>
       </c>
     </row>
     <row r="113">
@@ -3454,10 +3454,10 @@
         <v>0.8190929065449872</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>0.1443234582488593</v>
+        <v>0.1443234709050238</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.7636641410427741</v>
+        <v>0.7636641241505943</v>
       </c>
     </row>
     <row r="114">
@@ -3479,10 +3479,10 @@
         <v>0.9024974691223349</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0.05797461957992356</v>
+        <v>0.05797470065579535</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.8934073097189698</v>
+        <v>0.8934071727898472</v>
       </c>
     </row>
     <row r="115">
@@ -3560,8 +3560,33 @@
         <v>0.8267831983753214</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0.9785513195515015</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>-0.003456998036319825</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>1.006950014552054</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0.03558090139353665</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0.932463702352659</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G117"/>
+  <autoFilter ref="A1:G118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/isolated_excel/MPPM Recalculation.xlsx
+++ b/isolated_excel/MPPM Recalculation.xlsx
@@ -576,7 +576,7 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82295574656268</v>
+        <v>27.82296821150432</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>117</v>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.0205531804479008</v>
+        <v>0.02055318845689392</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>27.65201829092905</v>
+        <v>27.65203031222323</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6.462018290929048</v>
+        <v>6.462030312223231</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -619,7 +619,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -679,10 +679,10 @@
         <v>0.9631201026442409</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.02285950861465746</v>
+        <v>0.02285933094947112</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9558022014260387</v>
+        <v>0.9558025334615119</v>
       </c>
     </row>
     <row r="3">
@@ -704,10 +704,10 @@
         <v>0.9250752875147531</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.06935292250664793</v>
+        <v>-0.06935259164652441</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.154595775801609</v>
+        <v>1.154594954847014</v>
       </c>
     </row>
     <row r="4">
@@ -729,10 +729,10 @@
         <v>0.9976745395509637</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.0734133566970383</v>
+        <v>0.07341345219942963</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.8678926491403109</v>
+        <v>0.8678924947062119</v>
       </c>
     </row>
     <row r="5">
@@ -754,10 +754,10 @@
         <v>0.9797710949826629</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.04250426325590773</v>
+        <v>-0.04250443741575582</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.090752713599683</v>
+        <v>1.090753110395975</v>
       </c>
     </row>
     <row r="6">
@@ -779,10 +779,10 @@
         <v>0.9724380915636373</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3854463275870208</v>
+        <v>0.3854463634027958</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.5209794445625788</v>
+        <v>0.5209794176264478</v>
       </c>
     </row>
     <row r="7">
@@ -804,10 +804,10 @@
         <v>0.9876324120800218</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.001454655740082078</v>
+        <v>0.00145485704413173</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9970970242998092</v>
+        <v>0.9970966234437001</v>
       </c>
     </row>
     <row r="8">
@@ -829,10 +829,10 @@
         <v>0.9601089735562846</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1241699396708196</v>
+        <v>0.1241699230391513</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7912907042774466</v>
+        <v>0.7912907276911394</v>
       </c>
     </row>
     <row r="9">
@@ -854,10 +854,10 @@
         <v>0.9939038411792369</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.04356117246580737</v>
+        <v>0.0435612864237449</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9182568482101122</v>
+        <v>0.9182566476609884</v>
       </c>
     </row>
     <row r="10">
@@ -879,10 +879,10 @@
         <v>0.9599867759537827</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.05506401484726586</v>
+        <v>0.05506388809886431</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8983433937995275</v>
+        <v>0.8983436096416151</v>
       </c>
     </row>
     <row r="11">
@@ -904,10 +904,10 @@
         <v>0.9549146468467293</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1568496170350731</v>
+        <v>0.1568493836298717</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.7472160394229587</v>
+        <v>0.747216340938662</v>
       </c>
     </row>
     <row r="12">
@@ -929,10 +929,10 @@
         <v>0.9413715807084023</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.0288214196747697</v>
+        <v>-0.02882142237082763</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.060234200459706</v>
+        <v>1.060234206346271</v>
       </c>
     </row>
     <row r="13">
@@ -954,10 +954,10 @@
         <v>0.9781287914115532</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.03592278326681819</v>
+        <v>-0.03592220880918029</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.075911032173701</v>
+        <v>1.075909749984377</v>
       </c>
     </row>
     <row r="14">
@@ -979,10 +979,10 @@
         <v>0.8946259836989391</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2702847435166309</v>
+        <v>0.2702840090465197</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6197233156271994</v>
+        <v>0.6197240322675426</v>
       </c>
     </row>
     <row r="15">
@@ -1004,10 +1004,10 @@
         <v>1.077996580636878</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.01484796689881163</v>
+        <v>-0.01484781076548469</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1.030370661241828</v>
+        <v>1.030370334642165</v>
       </c>
     </row>
     <row r="16">
@@ -1029,10 +1029,10 @@
         <v>1.05283346576593</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.04301665282311129</v>
+        <v>-0.04301664938883587</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.091921051446883</v>
+        <v>1.091921043609845</v>
       </c>
     </row>
     <row r="17">
@@ -1054,10 +1054,10 @@
         <v>0.9923697257955202</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.02888718832462622</v>
+        <v>-0.02888710249012416</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1.060377814120852</v>
+        <v>1.060377626672002</v>
       </c>
     </row>
     <row r="18">
@@ -1079,10 +1079,10 @@
         <v>0.9535211430164198</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.122036107404736</v>
+        <v>0.1220363441559658</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.7943032404347704</v>
+        <v>0.7943029052366281</v>
       </c>
     </row>
     <row r="19">
@@ -1104,10 +1104,10 @@
         <v>0.9878038066806144</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-0.0606287579879855</v>
+        <v>-0.06062888790395171</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.133249350835984</v>
+        <v>1.133249664295047</v>
       </c>
     </row>
     <row r="20">
@@ -1129,10 +1129,10 @@
         <v>0.9295283057246148</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.03360087111769672</v>
+        <v>0.03360045538057688</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.9360396954912394</v>
+        <v>0.9360404484834103</v>
       </c>
     </row>
     <row r="21">
@@ -1154,10 +1154,10 @@
         <v>0.9378842120205459</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.1469147235425563</v>
+        <v>0.146914667857688</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.7602172920420806</v>
+        <v>0.7602173658620464</v>
       </c>
     </row>
     <row r="22">
@@ -1179,10 +1179,10 @@
         <v>0.9887123252954994</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.001211028569177319</v>
+        <v>0.001211235080261108</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.9975823355386397</v>
+        <v>0.9975819240135174</v>
       </c>
     </row>
     <row r="23">
@@ -1229,10 +1229,10 @@
         <v>0.9604566236375061</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-0.2240502996866476</v>
+        <v>-0.2240500250890657</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1.660859368313114</v>
+        <v>1.660858192804639</v>
       </c>
     </row>
     <row r="25">
@@ -1254,10 +1254,10 @@
         <v>1.208353246583336</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-0.1831362562963657</v>
+        <v>-0.1831368402774747</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.498651867231843</v>
+        <v>1.498654010025729</v>
       </c>
     </row>
     <row r="26">
@@ -1279,10 +1279,10 @@
         <v>0.857124786546162</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.07677880744130383</v>
+        <v>0.07677919618103357</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.8624759648359586</v>
+        <v>0.8624753420924767</v>
       </c>
     </row>
     <row r="27">
@@ -1304,10 +1304,10 @@
         <v>0.9387485503786788</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.07421907087205204</v>
+        <v>0.07421920498347312</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.8665912178308218</v>
+        <v>0.866591001450828</v>
       </c>
     </row>
     <row r="28">
@@ -1329,10 +1329,10 @@
         <v>0.9622415103954454</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.1640086642779561</v>
+        <v>0.1640088934931905</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.7380530410383462</v>
+        <v>0.7380527503653367</v>
       </c>
     </row>
     <row r="29">
@@ -1354,10 +1354,10 @@
         <v>0.9236868300043514</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.008019976847981169</v>
+        <v>0.008019330738912256</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.984150963497503</v>
+        <v>0.9841522251182816</v>
       </c>
     </row>
     <row r="30">
@@ -1379,10 +1379,10 @@
         <v>1.140325898830826</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-0.2507481618085182</v>
+        <v>-0.2507480822462205</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.781329933234055</v>
+        <v>1.781329554918854</v>
       </c>
     </row>
     <row r="31">
@@ -1404,10 +1404,10 @@
         <v>0.8726609769291781</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.2123872145602557</v>
+        <v>0.2123878988483392</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.68032636925465</v>
+        <v>0.6803256012841077</v>
       </c>
     </row>
     <row r="32">
@@ -1429,10 +1429,10 @@
         <v>0.971861873206222</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.0273398411515744</v>
+        <v>0.02733971441168226</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.9474836806515311</v>
+        <v>0.9474839144281196</v>
       </c>
     </row>
     <row r="33">
@@ -1454,10 +1454,10 @@
         <v>1.032451781203036</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-0.006188994530671899</v>
+        <v>-0.006189563197233738</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.012493855656376</v>
+        <v>1.012495014371446</v>
       </c>
     </row>
     <row r="34">
@@ -1479,10 +1479,10 @@
         <v>0.9636033160989426</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.03916182371534838</v>
+        <v>0.03916218137096039</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.9260482878867227</v>
+        <v>0.9260476504379854</v>
       </c>
     </row>
     <row r="35">
@@ -1504,10 +1504,10 @@
         <v>0.9580497393985004</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.1548229150566363</v>
+        <v>0.1548228046545519</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.7498410533013468</v>
+        <v>0.7498411966722931</v>
       </c>
     </row>
     <row r="36">
@@ -1529,10 +1529,10 @@
         <v>0.9311717640044544</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.07899691734969516</v>
+        <v>0.07899673370009652</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.8589336004545558</v>
+        <v>0.8589338928425112</v>
       </c>
     </row>
     <row r="37">
@@ -1554,10 +1554,10 @@
         <v>0.9422614020637016</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.08563267096236871</v>
+        <v>0.08563269372395554</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.8484655061631334</v>
+        <v>0.8484654705849473</v>
       </c>
     </row>
     <row r="38">
@@ -1579,10 +1579,10 @@
         <v>1.000784713254058</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.00480210260927838</v>
+        <v>0.004802430236670041</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.9904645350438945</v>
+        <v>0.9904638891392878</v>
       </c>
     </row>
     <row r="39">
@@ -1604,10 +1604,10 @@
         <v>1.187452557550319</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.1429665964522182</v>
+        <v>0.1429662599486818</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.7654783703495589</v>
+        <v>0.7654788210824029</v>
       </c>
     </row>
     <row r="40">
@@ -1629,10 +1629,10 @@
         <v>1.301695888634536</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-0.02395682257433085</v>
+        <v>-0.02395654342885645</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.049692126969056</v>
+        <v>1.0496915265516</v>
       </c>
     </row>
     <row r="41">
@@ -1654,10 +1654,10 @@
         <v>0.7856559601127485</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.1088011580457702</v>
+        <v>0.1088009317019811</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.813378443376611</v>
+        <v>0.8133787754527706</v>
       </c>
     </row>
     <row r="42">
@@ -1679,10 +1679,10 @@
         <v>0.9111424311350199</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.2146573116753359</v>
+        <v>0.2146572085391054</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.6777857946794612</v>
+        <v>0.6777859097807002</v>
       </c>
     </row>
     <row r="43">
@@ -1704,10 +1704,10 @@
         <v>0.9613795399637081</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.07059708952683108</v>
+        <v>0.07059732102863103</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.8724647377932303</v>
+        <v>0.8724643604765093</v>
       </c>
     </row>
     <row r="44">
@@ -1729,10 +1729,10 @@
         <v>0.8960977549701413</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.117606930723466</v>
+        <v>0.1176066277577954</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.8006115060428116</v>
+        <v>0.800611940109376</v>
       </c>
     </row>
     <row r="45">
@@ -1754,10 +1754,10 @@
         <v>0.870377843369757</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.2599917825318532</v>
+        <v>0.2599919433730087</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.6298897982664624</v>
+        <v>0.6298896374524239</v>
       </c>
     </row>
     <row r="46">
@@ -1779,10 +1779,10 @@
         <v>1.080556042343192</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.01196658441332676</v>
+        <v>0.01196672956150757</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.9764896752603323</v>
+        <v>0.9764893951410643</v>
       </c>
     </row>
     <row r="47">
@@ -1829,10 +1829,10 @@
         <v>0.8124073373168651</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.06921175375168209</v>
+        <v>0.06921152424538901</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.8747270391831757</v>
+        <v>0.8747274147035985</v>
       </c>
     </row>
     <row r="49">
@@ -1854,10 +1854,10 @@
         <v>0.9273208253828208</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>-0.02556746123653708</v>
+        <v>-0.02556732362456904</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1.053165065142114</v>
+        <v>1.053164767680605</v>
       </c>
     </row>
     <row r="50">
@@ -1879,10 +1879,10 @@
         <v>1.020502470298805</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>-0.004998199561433103</v>
+        <v>-0.004998126501084554</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1.010071847718824</v>
+        <v>1.010071699385036</v>
       </c>
     </row>
     <row r="51">
@@ -1904,10 +1904,10 @@
         <v>0.947050922347443</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.0557939828648184</v>
+        <v>0.05579383527242676</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.8971016074994462</v>
+        <v>0.8971018583161807</v>
       </c>
     </row>
     <row r="52">
@@ -1929,10 +1929,10 @@
         <v>0.9178444163991597</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>-0.02636946438879895</v>
+        <v>-0.02636932828224614</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1.054900815094783</v>
+        <v>1.054900520159737</v>
       </c>
     </row>
     <row r="53">
@@ -1954,10 +1954,10 @@
         <v>0.9012367883774663</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.1244546873627026</v>
+        <v>0.124454830941596</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.7908899950709026</v>
+        <v>0.7908897930972886</v>
       </c>
     </row>
     <row r="54">
@@ -1979,10 +1979,10 @@
         <v>0.9861767286709302</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.08228129943304796</v>
+        <v>0.08228103355163019</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.8537283259902673</v>
+        <v>0.8537287454571498</v>
       </c>
     </row>
     <row r="55">
@@ -2004,10 +2004,10 @@
         <v>0.9548946305726876</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.2316219268710247</v>
+        <v>0.2316223081379092</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.6592424666605762</v>
+        <v>0.6592420585041456</v>
       </c>
     </row>
     <row r="56">
@@ -2029,10 +2029,10 @@
         <v>0.9541320909722018</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>-0.0251717533870518</v>
+        <v>-0.0251720359416866</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1.052310225121558</v>
+        <v>1.052310835147502</v>
       </c>
     </row>
     <row r="57">
@@ -2054,10 +2054,10 @@
         <v>0.9418538915966996</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.1482099828948495</v>
+        <v>0.1482098009269623</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.7585031052999504</v>
+        <v>0.7585033457145824</v>
       </c>
     </row>
     <row r="58">
@@ -2079,10 +2079,10 @@
         <v>1.099935334897597</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>-0.07455890474406701</v>
+        <v>-0.07455866714113257</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1.167622454088943</v>
+        <v>1.167621854525306</v>
       </c>
     </row>
     <row r="59">
@@ -2104,10 +2104,10 @@
         <v>0.8733386651821466</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2341668361304334</v>
+        <v>0.2341667436536166</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.6565264926961334</v>
+        <v>0.656526591083945</v>
       </c>
     </row>
     <row r="60">
@@ -2129,10 +2129,10 @@
         <v>1.01400288589504</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.2780539093935128</v>
+        <v>0.2780537054365424</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.6122117403279266</v>
+        <v>0.6122119357263848</v>
       </c>
     </row>
     <row r="61">
@@ -2154,10 +2154,10 @@
         <v>0.9160517804201327</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>-0.09981033634665004</v>
+        <v>-0.09981006661035974</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.234047726429751</v>
+        <v>1.234046986880477</v>
       </c>
     </row>
     <row r="62">
@@ -2179,10 +2179,10 @@
         <v>1.112119386768055</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>-0.1674543610323084</v>
+        <v>-0.167454284996934</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1.442726136370509</v>
+        <v>1.44272587284572</v>
       </c>
     </row>
     <row r="63">
@@ -2204,10 +2204,10 @@
         <v>1.062685451631391</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>-0.004124858483746885</v>
+        <v>-0.004124936067363305</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1.008301042523602</v>
+        <v>1.008301199626932</v>
       </c>
     </row>
     <row r="64">
@@ -2229,10 +2229,10 @@
         <v>0.9296802682757126</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.119157305241937</v>
+        <v>0.1191569816697338</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.7983948597878558</v>
+        <v>0.7983953214539589</v>
       </c>
     </row>
     <row r="65">
@@ -2254,10 +2254,10 @@
         <v>1.200190656587331</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>-0.3202742385341527</v>
+        <v>-0.320273955026533</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2.164375155968217</v>
+        <v>2.164373350485772</v>
       </c>
     </row>
     <row r="66">
@@ -2279,10 +2279,10 @@
         <v>0.9963421662408478</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.006739561640910274</v>
+        <v>0.006739766771790112</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.9866559275352396</v>
+        <v>0.9866555254579906</v>
       </c>
     </row>
     <row r="67">
@@ -2304,10 +2304,10 @@
         <v>1.18803474289766</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>-0.1879708737784411</v>
+        <v>-0.1879711556529652</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1.516550183815672</v>
+        <v>1.516551236677128</v>
       </c>
     </row>
     <row r="68">
@@ -2329,10 +2329,10 @@
         <v>0.8382858229126688</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.1981663848721067</v>
+        <v>0.1981661828865631</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.6965715583184675</v>
+        <v>0.696571793173029</v>
       </c>
     </row>
     <row r="69">
@@ -2354,10 +2354,10 @@
         <v>1.086837917632202</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>-0.1689701420047741</v>
+        <v>-0.1689700016846472</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1.447993940397874</v>
+        <v>1.447993451407882</v>
       </c>
     </row>
     <row r="70">
@@ -2379,10 +2379,10 @@
         <v>1.213175071407492</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>-0.195534115260649</v>
+        <v>-0.1955341662868347</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1.545200133160607</v>
+        <v>1.545200329180545</v>
       </c>
     </row>
     <row r="71">
@@ -2404,10 +2404,10 @@
         <v>0.855814644350068</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1118707366172873</v>
+        <v>0.1118708943086355</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.8088936007475068</v>
+        <v>0.8088933713044769</v>
       </c>
     </row>
     <row r="72">
@@ -2429,10 +2429,10 @@
         <v>0.8969474204044003</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.2541548948752226</v>
+        <v>0.2541547170044127</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.635766506983844</v>
+        <v>0.6357666873193479</v>
       </c>
     </row>
     <row r="73">
@@ -2479,10 +2479,10 @@
         <v>0.8852560567072887</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3368685443762311</v>
+        <v>0.336868675327757</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.5595289869500825</v>
+        <v>0.5595288773339738</v>
       </c>
     </row>
     <row r="75">
@@ -2504,10 +2504,10 @@
         <v>1.050645569002066</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1883092769912784</v>
+        <v>0.1883094544534847</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.7081757069258796</v>
+        <v>0.708175495407889</v>
       </c>
     </row>
     <row r="76">
@@ -2529,10 +2529,10 @@
         <v>0.9304259309730823</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1966628825185215</v>
+        <v>0.1966624217283688</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.6983230205076165</v>
+        <v>0.6983235583041201</v>
       </c>
     </row>
     <row r="77">
@@ -2554,10 +2554,10 @@
         <v>0.9694982234937056</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>-0.001008053544630072</v>
+        <v>-0.001007984799151096</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1.002019159707699</v>
+        <v>1.002019021800121</v>
       </c>
     </row>
     <row r="78">
@@ -2579,10 +2579,10 @@
         <v>0.9913625810824932</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.3634366105814382</v>
+        <v>0.3634365666879342</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.537935365775992</v>
+        <v>0.5379354004118071</v>
       </c>
     </row>
     <row r="79">
@@ -2604,10 +2604,10 @@
         <v>0.8798812409728222</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1182104602933247</v>
+        <v>0.1182105733971262</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.7997475142654433</v>
+        <v>0.799747352481104</v>
       </c>
     </row>
     <row r="80">
@@ -2654,10 +2654,10 @@
         <v>1.032619118725376</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.05619630133525821</v>
+        <v>0.05619646510531018</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.896418303067284</v>
+        <v>0.896418025076464</v>
       </c>
     </row>
     <row r="82">
@@ -2679,10 +2679,10 @@
         <v>1.10263682294205</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>-0.1185779493598029</v>
+        <v>-0.1185781635581729</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1.287158941020093</v>
+        <v>1.287159566616985</v>
       </c>
     </row>
     <row r="83">
@@ -2704,10 +2704,10 @@
         <v>1.043418468810109</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>-0.06250726204228019</v>
+        <v>-0.06250717958217422</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1.137795404841957</v>
+        <v>1.137795204685276</v>
       </c>
     </row>
     <row r="84">
@@ -2779,10 +2779,10 @@
         <v>0.9672203593217011</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.242417441765066</v>
+        <v>0.2424173645114505</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.6478357655082039</v>
+        <v>0.6478358460731704</v>
       </c>
     </row>
     <row r="87">
@@ -2804,10 +2804,10 @@
         <v>0.9011908328520706</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.2858093057587894</v>
+        <v>0.2858095100706863</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.604848866220597</v>
+        <v>0.6048486740026853</v>
       </c>
     </row>
     <row r="88">
@@ -2829,10 +2829,10 @@
         <v>0.9386281887403397</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.1421813782406502</v>
+        <v>0.1421813644892354</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.7665312226847528</v>
+        <v>0.7665312411422225</v>
       </c>
     </row>
     <row r="89">
@@ -2854,10 +2854,10 @@
         <v>1.086982276900574</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>-0.04376030793594532</v>
+        <v>-0.04376038890822365</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>1.093620057303434</v>
+        <v>1.09362024251415</v>
       </c>
     </row>
     <row r="90">
@@ -2879,10 +2879,10 @@
         <v>0.9077465777794721</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.2688711796833401</v>
+        <v>0.2688710911304248</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.6211048686740451</v>
+        <v>0.6211049553663011</v>
       </c>
     </row>
     <row r="91">
@@ -2904,10 +2904,10 @@
         <v>0.9319221176611617</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1269429881861628</v>
+        <v>0.1269431366228349</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.7874012656570388</v>
+        <v>0.787401058230041</v>
       </c>
     </row>
     <row r="92">
@@ -2929,10 +2929,10 @@
         <v>0.9760924573374677</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>-0.05277639146240565</v>
+        <v>-0.05277657397651536</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>1.114538236224359</v>
+        <v>1.11453866573015</v>
       </c>
     </row>
     <row r="93">
@@ -2954,10 +2954,10 @@
         <v>0.9531969858300583</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.02008192895097527</v>
+        <v>0.02008212771048568</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.9610143928788231</v>
+        <v>0.9610140183781306</v>
       </c>
     </row>
     <row r="94">
@@ -2979,10 +2979,10 @@
         <v>0.9586163156807694</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.0174282162006334</v>
+        <v>0.0174281509928309</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.9660340728263759</v>
+        <v>0.9660341966542078</v>
       </c>
     </row>
     <row r="95">
@@ -3004,10 +3004,10 @@
         <v>1.018385718385046</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.09321453028446558</v>
+        <v>0.09321465627039194</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.8367374537752976</v>
+        <v>0.8367372609181372</v>
       </c>
     </row>
     <row r="96">
@@ -3029,10 +3029,10 @@
         <v>0.8921825152855977</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04135284406682982</v>
+        <v>0.0413529545447211</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.9221555513469486</v>
+        <v>0.9221553556826546</v>
       </c>
     </row>
     <row r="97">
@@ -3054,10 +3054,10 @@
         <v>1.049436799471192</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>-0.02857691450021882</v>
+        <v>-0.02857701884229569</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1.059700550131759</v>
+        <v>1.059700777779992</v>
       </c>
     </row>
     <row r="98">
@@ -3079,10 +3079,10 @@
         <v>0.9465483128657197</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>-0.1058900206097576</v>
+        <v>-0.1058901224691788</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>1.250887105297516</v>
+        <v>1.250887390306433</v>
       </c>
     </row>
     <row r="99">
@@ -3104,10 +3104,10 @@
         <v>1.026615030088406</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.0403930563602144</v>
+        <v>0.04039312006754003</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.9238577576568019</v>
+        <v>0.9238576445139829</v>
       </c>
     </row>
     <row r="100">
@@ -3129,10 +3129,10 @@
         <v>1.122982133980397</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>-0.132324990602127</v>
+        <v>-0.1323249824993521</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1.328268341648021</v>
+        <v>1.328268316839978</v>
       </c>
     </row>
     <row r="101">
@@ -3154,10 +3154,10 @@
         <v>1.013702149839987</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.004982481462220356</v>
+        <v>0.004982410538207693</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.9901090207404083</v>
+        <v>0.9901091604891371</v>
       </c>
     </row>
     <row r="102">
@@ -3204,10 +3204,10 @@
         <v>0.9055585326855982</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0.1692515691786884</v>
+        <v>0.1692516823827925</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.7314490448986909</v>
+        <v>0.7314489032644627</v>
       </c>
     </row>
     <row r="104">
@@ -3229,10 +3229,10 @@
         <v>0.9565816763960454</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0.1258307069145082</v>
+        <v>0.1258307915494528</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.78895788391466</v>
+        <v>0.7889577652939849</v>
       </c>
     </row>
     <row r="105">
@@ -3254,10 +3254,10 @@
         <v>0.9606567708776664</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>-0.0207454681313487</v>
+        <v>-0.02074555055982463</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>1.042818722621746</v>
+        <v>1.042818898179716</v>
       </c>
     </row>
     <row r="106">
@@ -3279,10 +3279,10 @@
         <v>0.930810829949856</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.07125119707459349</v>
+        <v>0.07125110299903326</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.8713996065879218</v>
+        <v>0.8713997596377708</v>
       </c>
     </row>
     <row r="107">
@@ -3304,10 +3304,10 @@
         <v>0.9547673052543396</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0.0852718395616765</v>
+        <v>0.08527167560685012</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.8490297959212769</v>
+        <v>0.8490300524515936</v>
       </c>
     </row>
     <row r="108">
@@ -3329,10 +3329,10 @@
         <v>0.9951162119266498</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>-0.1258828209996035</v>
+        <v>-0.1258826889444383</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>1.308762036967603</v>
+        <v>1.308761641531495</v>
       </c>
     </row>
     <row r="109">
@@ -3404,10 +3404,10 @@
         <v>1.015374766883167</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>-0.07293472316669725</v>
+        <v>-0.07293464314527709</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>1.163534781536039</v>
+        <v>1.163534580670585</v>
       </c>
     </row>
     <row r="112">
@@ -3429,10 +3429,10 @@
         <v>1.107555373472521</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>-0.0156925888464382</v>
+        <v>-0.01569258749190239</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>1.032139716417717</v>
+        <v>1.032139713576999</v>
       </c>
     </row>
     <row r="113">
@@ -3454,10 +3454,10 @@
         <v>0.8190929065449872</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>0.1443234709050238</v>
+        <v>0.1443234582488593</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.7636641241505943</v>
+        <v>0.7636641410427741</v>
       </c>
     </row>
     <row r="114">
@@ -3479,10 +3479,10 @@
         <v>0.9024974691223349</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0.05797470065579535</v>
+        <v>0.05797461957992356</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.8934071727898472</v>
+        <v>0.8934073097189698</v>
       </c>
     </row>
     <row r="115">

--- a/isolated_excel/MPPM Recalculation.xlsx
+++ b/isolated_excel/MPPM Recalculation.xlsx
@@ -576,7 +576,7 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82296821150432</v>
+        <v>27.82296668891937</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>117</v>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.02055318845689392</v>
+        <v>0.0205531874786004</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>27.65203031222323</v>
+        <v>27.65202884382967</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6.462030312223231</v>
+        <v>6.462028843829668</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -619,7 +619,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -679,10 +679,10 @@
         <v>0.9631201026442409</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.02285933094947112</v>
+        <v>0.02285951277100851</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9558025334615119</v>
+        <v>0.9558021936583063</v>
       </c>
     </row>
     <row r="3">
@@ -704,10 +704,10 @@
         <v>0.9250752875147531</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.06935259164652441</v>
+        <v>-0.06935257931854133</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.154594954847014</v>
+        <v>1.154594924257928</v>
       </c>
     </row>
     <row r="4">
@@ -729,10 +729,10 @@
         <v>0.9976745395509637</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.07341345219942963</v>
+        <v>0.07341324717236564</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.8678924947062119</v>
+        <v>0.8678928262494783</v>
       </c>
     </row>
     <row r="5">
@@ -754,10 +754,10 @@
         <v>0.9797710949826629</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.04250443741575582</v>
+        <v>-0.04250434844501383</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.090753110395975</v>
+        <v>1.090752907689866</v>
       </c>
     </row>
     <row r="6">
@@ -779,10 +779,10 @@
         <v>0.9724380915636373</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3854463634027958</v>
+        <v>0.3854463275870208</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.5209794176264478</v>
+        <v>0.5209794445625788</v>
       </c>
     </row>
     <row r="7">
@@ -804,10 +804,10 @@
         <v>0.9876324120800218</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.00145485704413173</v>
+        <v>0.001454588671257362</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9970966234437001</v>
+        <v>0.9970971578537986</v>
       </c>
     </row>
     <row r="8">
@@ -829,10 +829,10 @@
         <v>0.9601089735562846</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1241699230391513</v>
+        <v>0.124170148900882</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7912907276911394</v>
+        <v>0.791290409728106</v>
       </c>
     </row>
     <row r="9">
@@ -854,10 +854,10 @@
         <v>0.9939038411792369</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.0435612864237449</v>
+        <v>0.04356152472008823</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9182566476609884</v>
+        <v>0.9182562282948634</v>
       </c>
     </row>
     <row r="10">
@@ -879,10 +879,10 @@
         <v>0.9599867759537827</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.05506388809886431</v>
+        <v>0.0550633046523048</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8983436096416151</v>
+        <v>0.8983446032040505</v>
       </c>
     </row>
     <row r="11">
@@ -904,10 +904,10 @@
         <v>0.9549146468467293</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1568493836298717</v>
+        <v>0.1568499756297945</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.747216340938662</v>
+        <v>0.7472155761862527</v>
       </c>
     </row>
     <row r="12">
@@ -929,10 +929,10 @@
         <v>0.9413715807084023</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.02882142237082763</v>
+        <v>-0.0288213234351804</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.060234206346271</v>
+        <v>1.060233990330506</v>
       </c>
     </row>
     <row r="13">
@@ -954,10 +954,10 @@
         <v>0.9781287914115532</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.03592220880918029</v>
+        <v>-0.03592239106832296</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.075909749984377</v>
+        <v>1.075910156786496</v>
       </c>
     </row>
     <row r="14">
@@ -979,10 +979,10 @@
         <v>0.8946259836989391</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2702840090465197</v>
+        <v>0.2702838821342943</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6197240322675426</v>
+        <v>0.6197241560990122</v>
       </c>
     </row>
     <row r="15">
@@ -1029,10 +1029,10 @@
         <v>1.05283346576593</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.04301664938883587</v>
+        <v>-0.04301648971692962</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.091921043609845</v>
+        <v>1.091920679237631</v>
       </c>
     </row>
     <row r="17">
@@ -1054,10 +1054,10 @@
         <v>0.9923697257955202</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.02888710249012416</v>
+        <v>-0.02888726451950696</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1.060377626672002</v>
+        <v>1.060377980518349</v>
       </c>
     </row>
     <row r="18">
@@ -1079,10 +1079,10 @@
         <v>0.9535211430164198</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.1220363441559658</v>
+        <v>0.1220361723436048</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.7943029052366281</v>
+        <v>0.7943031484927214</v>
       </c>
     </row>
     <row r="19">
@@ -1104,10 +1104,10 @@
         <v>0.9878038066806144</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-0.06062888790395171</v>
+        <v>-0.06062882062502617</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.133249664295047</v>
+        <v>1.133249501965568</v>
       </c>
     </row>
     <row r="20">
@@ -1129,10 +1129,10 @@
         <v>0.9295283057246148</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.03360045538057688</v>
+        <v>0.03360086564046827</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.9360404484834103</v>
+        <v>0.9360397054117097</v>
       </c>
     </row>
     <row r="21">
@@ -1154,10 +1154,10 @@
         <v>0.9378842120205459</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.146914667857688</v>
+        <v>0.1469144638086999</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.7602173658620464</v>
+        <v>0.7602176363645171</v>
       </c>
     </row>
     <row r="22">
@@ -1179,10 +1179,10 @@
         <v>0.9887123252954994</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.001211235080261108</v>
+        <v>0.001211372421218604</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.9975819240135174</v>
+        <v>0.9975816503273588</v>
       </c>
     </row>
     <row r="23">
@@ -1204,10 +1204,10 @@
         <v>1.152111238395737</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-0.2497684599418704</v>
+        <v>-0.2497686660171804</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.776680614491729</v>
+        <v>1.776681590537496</v>
       </c>
     </row>
     <row r="24">
@@ -1229,10 +1229,10 @@
         <v>0.9604566236375061</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-0.2240500250890657</v>
+        <v>-0.2240499335565385</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1.660858192804639</v>
+        <v>1.660857800968759</v>
       </c>
     </row>
     <row r="25">
@@ -1254,10 +1254,10 @@
         <v>1.208353246583336</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-0.1831368402774747</v>
+        <v>-0.183136818674309</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.498654010025729</v>
+        <v>1.498653930757447</v>
       </c>
     </row>
     <row r="26">
@@ -1279,10 +1279,10 @@
         <v>0.857124786546162</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.07677919618103357</v>
+        <v>0.07677932950184241</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.8624753420924767</v>
+        <v>0.8624751285187203</v>
       </c>
     </row>
     <row r="27">
@@ -1304,10 +1304,10 @@
         <v>0.9387485503786788</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.07421920498347312</v>
+        <v>0.0742187827420373</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.866591001450828</v>
+        <v>0.8665916827100026</v>
       </c>
     </row>
     <row r="28">
@@ -1329,10 +1329,10 @@
         <v>0.9622415103954454</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.1640088934931905</v>
+        <v>0.1640089139689633</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.7380527503653367</v>
+        <v>0.7380527243995555</v>
       </c>
     </row>
     <row r="29">
@@ -1354,10 +1354,10 @@
         <v>0.9236868300043514</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.008019330738912256</v>
+        <v>0.008019438853789751</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.9841522251182816</v>
+        <v>0.9841520140082822</v>
       </c>
     </row>
     <row r="30">
@@ -1379,10 +1379,10 @@
         <v>1.140325898830826</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-0.2507480822462205</v>
+        <v>-0.2507479758447347</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.781329554918854</v>
+        <v>1.781329048984691</v>
       </c>
     </row>
     <row r="31">
@@ -1404,10 +1404,10 @@
         <v>0.8726609769291781</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.2123878988483392</v>
+        <v>0.2123873006459764</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.6803256012841077</v>
+        <v>0.6803262726413255</v>
       </c>
     </row>
     <row r="32">
@@ -1429,10 +1429,10 @@
         <v>0.971861873206222</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.02733971441168226</v>
+        <v>0.02733960688604764</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.9474839144281196</v>
+        <v>0.9474841127633418</v>
       </c>
     </row>
     <row r="33">
@@ -1454,10 +1454,10 @@
         <v>1.032451781203036</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-0.006189563197233738</v>
+        <v>-0.006188539879471766</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.012495014371446</v>
+        <v>1.012492929260456</v>
       </c>
     </row>
     <row r="34">
@@ -1479,10 +1479,10 @@
         <v>0.9636033160989426</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.03916218137096039</v>
+        <v>0.03916215890643548</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.9260476504379854</v>
+        <v>0.9260476904764348</v>
       </c>
     </row>
     <row r="35">
@@ -1504,10 +1504,10 @@
         <v>0.9580497393985004</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.1548228046545519</v>
+        <v>0.1548224983867503</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.7498411966722931</v>
+        <v>0.7498415943996419</v>
       </c>
     </row>
     <row r="36">
@@ -1529,10 +1529,10 @@
         <v>0.9311717640044544</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.07899673370009652</v>
+        <v>0.0789967110436296</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.8589338928425112</v>
+        <v>0.8589339289138122</v>
       </c>
     </row>
     <row r="37">
@@ -1554,10 +1554,10 @@
         <v>0.9422614020637016</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.08563269372395554</v>
+        <v>0.0856324937591233</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.8484654705849473</v>
+        <v>0.8484657831460987</v>
       </c>
     </row>
     <row r="38">
@@ -1579,10 +1579,10 @@
         <v>1.000784713254058</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.004802430236670041</v>
+        <v>0.004802185006011594</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.9904638891392878</v>
+        <v>0.9904643726018937</v>
       </c>
     </row>
     <row r="39">
@@ -1604,10 +1604,10 @@
         <v>1.187452557550319</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.1429662599486818</v>
+        <v>0.1429666080643739</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.7654788210824029</v>
+        <v>0.7654783547955543</v>
       </c>
     </row>
     <row r="40">
@@ -1629,10 +1629,10 @@
         <v>1.301695888634536</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-0.02395654342885645</v>
+        <v>-0.02395682427677925</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.0496915265516</v>
+        <v>1.049692130630875</v>
       </c>
     </row>
     <row r="41">
@@ -1654,10 +1654,10 @@
         <v>0.7856559601127485</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.1088009317019811</v>
+        <v>0.1088011659673027</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.8133787754527706</v>
+        <v>0.8133784317546828</v>
       </c>
     </row>
     <row r="42">
@@ -1679,10 +1679,10 @@
         <v>0.9111424311350199</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.2146572085391054</v>
+        <v>0.2146571287808294</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.6777859097807002</v>
+        <v>0.6777859987918889</v>
       </c>
     </row>
     <row r="43">
@@ -1704,10 +1704,10 @@
         <v>0.9613795399637081</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.07059732102863103</v>
+        <v>0.07059710479247427</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.8724643604765093</v>
+        <v>0.8724647129122826</v>
       </c>
     </row>
     <row r="44">
@@ -1729,10 +1729,10 @@
         <v>0.8960977549701413</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.1176066277577954</v>
+        <v>0.1176070554659563</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.800611940109376</v>
+        <v>0.8006113273211992</v>
       </c>
     </row>
     <row r="45">
@@ -1754,10 +1754,10 @@
         <v>0.870377843369757</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.2599919433730087</v>
+        <v>0.2599920771093882</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.6298896374524239</v>
+        <v>0.6298895037386384</v>
       </c>
     </row>
     <row r="46">
@@ -1779,10 +1779,10 @@
         <v>1.080556042343192</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.01196672956150757</v>
+        <v>0.01196651098106316</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.9764893951410643</v>
+        <v>0.9764898169761875</v>
       </c>
     </row>
     <row r="47">
@@ -1804,10 +1804,10 @@
         <v>1.055384676976521</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-0.07364841033159564</v>
+        <v>-0.07364833424445749</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1.165328311617677</v>
+        <v>1.165328120186073</v>
       </c>
     </row>
     <row r="48">
@@ -1829,10 +1829,10 @@
         <v>0.8124073373168651</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.06921152424538901</v>
+        <v>0.06921181966408096</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.8747274147035985</v>
+        <v>0.8747269313367142</v>
       </c>
     </row>
     <row r="49">
@@ -1854,10 +1854,10 @@
         <v>0.9273208253828208</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>-0.02556732362456904</v>
+        <v>-0.02556788504837204</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1.053164767680605</v>
+        <v>1.053165981252962</v>
       </c>
     </row>
     <row r="50">
@@ -1879,10 +1879,10 @@
         <v>1.020502470298805</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>-0.004998126501084554</v>
+        <v>-0.004997906952991293</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1.010071699385036</v>
+        <v>1.010071253638655</v>
       </c>
     </row>
     <row r="51">
@@ -1904,10 +1904,10 @@
         <v>0.947050922347443</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.05579383527242676</v>
+        <v>0.05579383115505432</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.8971018583161807</v>
+        <v>0.8971018653131955</v>
       </c>
     </row>
     <row r="52">
@@ -1929,10 +1929,10 @@
         <v>0.9178444163991597</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>-0.02636932828224614</v>
+        <v>-0.02636918664632026</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1.054900520159737</v>
+        <v>1.05490021324299</v>
       </c>
     </row>
     <row r="53">
@@ -1954,10 +1954,10 @@
         <v>0.9012367883774663</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.124454830941596</v>
+        <v>0.1244542298225215</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.7908897930972886</v>
+        <v>0.7908906386969669</v>
       </c>
     </row>
     <row r="54">
@@ -1979,10 +1979,10 @@
         <v>0.9861767286709302</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.08228103355163019</v>
+        <v>0.08228150672390133</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.8537287454571498</v>
+        <v>0.8537279989587968</v>
       </c>
     </row>
     <row r="55">
@@ -2004,10 +2004,10 @@
         <v>0.9548946305726876</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.2316223081379092</v>
+        <v>0.2316220448510509</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.6592420585041456</v>
+        <v>0.6592423403597518</v>
       </c>
     </row>
     <row r="56">
@@ -2029,10 +2029,10 @@
         <v>0.9541320909722018</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>-0.0251720359416866</v>
+        <v>-0.02517194256058053</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1.052310835147502</v>
+        <v>1.052310633540779</v>
       </c>
     </row>
     <row r="57">
@@ -2054,10 +2054,10 @@
         <v>0.9418538915966996</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.1482098009269623</v>
+        <v>0.1482101939907232</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.7585033457145824</v>
+        <v>0.7585028264017802</v>
       </c>
     </row>
     <row r="58">
@@ -2079,10 +2079,10 @@
         <v>1.099935334897597</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>-0.07455866714113257</v>
+        <v>-0.07455889836317886</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1.167621854525306</v>
+        <v>1.167622437987501</v>
       </c>
     </row>
     <row r="59">
@@ -2104,10 +2104,10 @@
         <v>0.8733386651821466</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2341667436536166</v>
+        <v>0.2341668144754319</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.656526591083945</v>
+        <v>0.6565265157352919</v>
       </c>
     </row>
     <row r="60">
@@ -2129,10 +2129,10 @@
         <v>1.01400288589504</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.2780537054365424</v>
+        <v>0.2780533640448715</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.6122119357263848</v>
+        <v>0.6122122627926709</v>
       </c>
     </row>
     <row r="61">
@@ -2154,10 +2154,10 @@
         <v>0.9160517804201327</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>-0.09981006661035974</v>
+        <v>-0.09980996105649786</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.234046986880477</v>
+        <v>1.234046697478435</v>
       </c>
     </row>
     <row r="62">
@@ -2179,10 +2179,10 @@
         <v>1.112119386768055</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>-0.167454284996934</v>
+        <v>-0.1674545455137538</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1.44272587284572</v>
+        <v>1.442726775749971</v>
       </c>
     </row>
     <row r="63">
@@ -2204,10 +2204,10 @@
         <v>1.062685451631391</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>-0.004124936067363305</v>
+        <v>-0.004124702671098213</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1.008301199626932</v>
+        <v>1.008300727010115</v>
       </c>
     </row>
     <row r="64">
@@ -2229,10 +2229,10 @@
         <v>0.9296802682757126</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.1191569816697338</v>
+        <v>0.1191572266889214</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.7983953214539589</v>
+        <v>0.7983949718656311</v>
       </c>
     </row>
     <row r="65">
@@ -2254,10 +2254,10 @@
         <v>1.200190656587331</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>-0.320273955026533</v>
+        <v>-0.3202740504457099</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2.164373350485772</v>
+        <v>2.164373958150488</v>
       </c>
     </row>
     <row r="66">
@@ -2279,10 +2279,10 @@
         <v>0.9963421662408478</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.006739766771790112</v>
+        <v>0.006739663510413774</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.9866555254579906</v>
+        <v>0.9866557278606901</v>
       </c>
     </row>
     <row r="67">
@@ -2304,10 +2304,10 @@
         <v>1.18803474289766</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>-0.1879711556529652</v>
+        <v>-0.1879711236481391</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1.516551236677128</v>
+        <v>1.516551117132222</v>
       </c>
     </row>
     <row r="68">
@@ -2329,10 +2329,10 @@
         <v>0.8382858229126688</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.1981661828865631</v>
+        <v>0.1981660059320538</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.696571793173029</v>
+        <v>0.6965719989233646</v>
       </c>
     </row>
     <row r="69">
@@ -2354,10 +2354,10 @@
         <v>1.086837917632202</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>-0.1689700016846472</v>
+        <v>-0.1689697210443043</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1.447993451407882</v>
+        <v>1.447992473428329</v>
       </c>
     </row>
     <row r="70">
@@ -2379,10 +2379,10 @@
         <v>1.213175071407492</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>-0.1955341662868347</v>
+        <v>-0.195534268339187</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1.545200329180545</v>
+        <v>1.545200721220459</v>
       </c>
     </row>
     <row r="71">
@@ -2404,10 +2404,10 @@
         <v>0.855814644350068</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1118708943086355</v>
+        <v>0.1118709731543095</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.8088933713044769</v>
+        <v>0.8088932565829987</v>
       </c>
     </row>
     <row r="72">
@@ -2429,10 +2429,10 @@
         <v>0.8969474204044003</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.2541547170044127</v>
+        <v>0.2541550535446946</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.6357666873193479</v>
+        <v>0.6357663461158088</v>
       </c>
     </row>
     <row r="73">
@@ -2454,10 +2454,10 @@
         <v>1.126011828926274</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>-0.1364413766930278</v>
+        <v>-0.1364416696577458</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1.340961624379565</v>
+        <v>1.340962534230114</v>
       </c>
     </row>
     <row r="74">
@@ -2479,10 +2479,10 @@
         <v>0.8852560567072887</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.336868675327757</v>
+        <v>0.3368688062792828</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.5595288773339738</v>
+        <v>0.5595287677178974</v>
       </c>
     </row>
     <row r="75">
@@ -2504,10 +2504,10 @@
         <v>1.050645569002066</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1883094544534847</v>
+        <v>0.1883094360078374</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.708175495407889</v>
+        <v>0.7081755173933334</v>
       </c>
     </row>
     <row r="76">
@@ -2529,10 +2529,10 @@
         <v>0.9304259309730823</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1966624217283688</v>
+        <v>0.1966623230859119</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.6983235583041201</v>
+        <v>0.6983236734315925</v>
       </c>
     </row>
     <row r="77">
@@ -2554,10 +2554,10 @@
         <v>0.9694982234937056</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>-0.001007984799151096</v>
+        <v>-0.001007915914793878</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1.002019021800121</v>
+        <v>1.002018883613973</v>
       </c>
     </row>
     <row r="78">
@@ -2579,10 +2579,10 @@
         <v>0.9913625810824932</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.3634365666879342</v>
+        <v>0.3634363347660106</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.5379354004118071</v>
+        <v>0.5379355834185531</v>
       </c>
     </row>
     <row r="79">
@@ -2604,10 +2604,10 @@
         <v>0.8798812409728222</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1182105733971262</v>
+        <v>0.11821058535379</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.799747352481104</v>
+        <v>0.7997473353782248</v>
       </c>
     </row>
     <row r="80">
@@ -2629,10 +2629,10 @@
         <v>0.9387194711195235</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1046522093279367</v>
+        <v>0.1046522187941983</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.8194998322662915</v>
+        <v>0.8194998182209665</v>
       </c>
     </row>
     <row r="81">
@@ -2654,10 +2654,10 @@
         <v>1.032619118725376</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.05619646510531018</v>
+        <v>0.05619646970695968</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.896418025076464</v>
+        <v>0.8964180172654143</v>
       </c>
     </row>
     <row r="82">
@@ -2679,10 +2679,10 @@
         <v>1.10263682294205</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>-0.1185781635581729</v>
+        <v>-0.1185781727513269</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1.287159566616985</v>
+        <v>1.287159593466912</v>
       </c>
     </row>
     <row r="83">
@@ -2704,10 +2704,10 @@
         <v>1.043418468810109</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>-0.06250717958217422</v>
+        <v>-0.06250709712205382</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1.137795204685276</v>
+        <v>1.137795004528613</v>
       </c>
     </row>
     <row r="84">
@@ -2729,10 +2729,10 @@
         <v>0.8396361081156987</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.1468857564818131</v>
+        <v>0.1468859441272559</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.7602556943649784</v>
+        <v>0.7602554455895785</v>
       </c>
     </row>
     <row r="85">
@@ -2754,10 +2754,10 @@
         <v>0.9149756157506371</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.05893439166961034</v>
+        <v>0.05893405480119052</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.8917885525575281</v>
+        <v>0.8917891199497032</v>
       </c>
     </row>
     <row r="86">
@@ -2779,10 +2779,10 @@
         <v>0.9672203593217011</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.2424173645114505</v>
+        <v>0.2424176337275741</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.6478358460731704</v>
+        <v>0.647835565317599</v>
       </c>
     </row>
     <row r="87">
@@ -2804,10 +2804,10 @@
         <v>0.9011908328520706</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.2858095100706863</v>
+        <v>0.2858094301189487</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.6048486740026853</v>
+        <v>0.6048487492217697</v>
       </c>
     </row>
     <row r="88">
@@ -2854,10 +2854,10 @@
         <v>1.086982276900574</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>-0.04376038890822365</v>
+        <v>-0.04376013487480812</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>1.09362024251415</v>
+        <v>1.093619661454818</v>
       </c>
     </row>
     <row r="90">
@@ -2879,10 +2879,10 @@
         <v>0.9077465777794721</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.2688710911304248</v>
+        <v>0.2688708425967037</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.6211049553663011</v>
+        <v>0.6211051986779695</v>
       </c>
     </row>
     <row r="91">
@@ -2904,10 +2904,10 @@
         <v>0.9319221176611617</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1269431366228349</v>
+        <v>0.1269430579748985</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.787401058230041</v>
+        <v>0.7874011681335008</v>
       </c>
     </row>
     <row r="92">
@@ -2929,10 +2929,10 @@
         <v>0.9760924573374677</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>-0.05277657397651536</v>
+        <v>-0.05277651204904255</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>1.11453866573015</v>
+        <v>1.114538519997782</v>
       </c>
     </row>
     <row r="93">
@@ -2954,10 +2954,10 @@
         <v>0.9531969858300583</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.02008212771048568</v>
+        <v>0.02008206101966881</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.9610140183781306</v>
+        <v>0.9610141440362799</v>
       </c>
     </row>
     <row r="94">
@@ -2979,10 +2979,10 @@
         <v>0.9586163156807694</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.0174281509928309</v>
+        <v>0.01742821508364489</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.9660341966542078</v>
+        <v>0.9660340749475063</v>
       </c>
     </row>
     <row r="95">
@@ -3004,10 +3004,10 @@
         <v>1.018385718385046</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.09321465627039194</v>
+        <v>0.09321446141964707</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.8367372609181372</v>
+        <v>0.8367375591924444</v>
       </c>
     </row>
     <row r="96">
@@ -3029,10 +3029,10 @@
         <v>0.8921825152855977</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.0413529545447211</v>
+        <v>0.04135295931038252</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.9221553556826546</v>
+        <v>0.9221553472423267</v>
       </c>
     </row>
     <row r="97">
@@ -3054,10 +3054,10 @@
         <v>1.049436799471192</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>-0.02857701884229569</v>
+        <v>-0.02857691133769347</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1.059700777779992</v>
+        <v>1.059700543231924</v>
       </c>
     </row>
     <row r="98">
@@ -3079,10 +3079,10 @@
         <v>0.9465483128657197</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>-0.1058901224691788</v>
+        <v>-0.1058901794305278</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>1.250887390306433</v>
+        <v>1.250887549687828</v>
       </c>
     </row>
     <row r="99">
@@ -3104,10 +3104,10 @@
         <v>1.026615030088406</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.04039312006754003</v>
+        <v>0.04039305893354816</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.9238576445139829</v>
+        <v>0.9238577530866169</v>
       </c>
     </row>
     <row r="100">
@@ -3129,10 +3129,10 @@
         <v>1.122982133980397</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>-0.1323249824993521</v>
+        <v>-0.132324937470998</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1.328268316839978</v>
+        <v>1.328268178977921</v>
       </c>
     </row>
     <row r="101">
@@ -3154,10 +3154,10 @@
         <v>1.013702149839987</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.004982410538207693</v>
+        <v>0.004982481462220356</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.9901091604891371</v>
+        <v>0.9901090207404083</v>
       </c>
     </row>
     <row r="102">
@@ -3179,10 +3179,10 @@
         <v>0.8850712241425256</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>0.2406354069759602</v>
+        <v>0.24063554742098</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.649698190191852</v>
+        <v>0.6496980430948739</v>
       </c>
     </row>
     <row r="103">
@@ -3204,10 +3204,10 @@
         <v>0.9055585326855982</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0.1692516823827925</v>
+        <v>0.1692515500187184</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.7314489032644627</v>
+        <v>0.7314490688705075</v>
       </c>
     </row>
     <row r="104">
@@ -3229,10 +3229,10 @@
         <v>0.9565816763960454</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0.1258307915494528</v>
+        <v>0.1258305979143173</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.7889577652939849</v>
+        <v>0.7889580366846491</v>
       </c>
     </row>
     <row r="105">
@@ -3254,10 +3254,10 @@
         <v>0.9606567708776664</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>-0.02074555055982463</v>
+        <v>-0.0207454681313487</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>1.042818898179716</v>
+        <v>1.042818722621746</v>
       </c>
     </row>
     <row r="106">
@@ -3279,10 +3279,10 @@
         <v>0.930810829949856</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.07125110299903326</v>
+        <v>0.07125119707459349</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.8713997596377708</v>
+        <v>0.8713996065879218</v>
       </c>
     </row>
     <row r="107">
@@ -3329,10 +3329,10 @@
         <v>0.9951162119266498</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>-0.1258826889444383</v>
+        <v>-0.1258827644807442</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>1.308761641531495</v>
+        <v>1.308761867723177</v>
       </c>
     </row>
     <row r="109">
@@ -3354,10 +3354,10 @@
         <v>0.9987769482420827</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>0.05373090631056576</v>
+        <v>0.05373099736807707</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.9006178773401333</v>
+        <v>0.9006177216874682</v>
       </c>
     </row>
     <row r="110">
@@ -3404,10 +3404,10 @@
         <v>1.015374766883167</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>-0.07293464314527709</v>
+        <v>-0.07293472316669725</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>1.163534580670585</v>
+        <v>1.163534781536039</v>
       </c>
     </row>
     <row r="112">
@@ -3429,10 +3429,10 @@
         <v>1.107555373472521</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>-0.01569258749190239</v>
+        <v>-0.0156925888464382</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>1.032139713576999</v>
+        <v>1.032139716417717</v>
       </c>
     </row>
     <row r="113">
@@ -3454,10 +3454,10 @@
         <v>0.8190929065449872</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>0.1443234582488593</v>
+        <v>0.1443234709050238</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.7636641410427741</v>
+        <v>0.7636641241505943</v>
       </c>
     </row>
     <row r="114">
@@ -3479,10 +3479,10 @@
         <v>0.9024974691223349</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0.05797461957992356</v>
+        <v>0.05797470065579535</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.8934073097189698</v>
+        <v>0.8934071727898472</v>
       </c>
     </row>
     <row r="115">
